--- a/Исходный_Шаблон_Весь_период.xlsx
+++ b/Исходный_Шаблон_Весь_период.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ЭтаКнига" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORK\Repository\github.com\daily_duty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58C92827-280E-4CB0-BE4B-E7BDA31FB74A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF190B9B-E997-49DE-8FA8-D5AF3F26F770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25080" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="721" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="495" windowWidth="25065" windowHeight="13380" tabRatio="721" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="График" sheetId="12" r:id="rId1"/>
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="74">
   <si>
     <t>=</t>
   </si>
@@ -192,9 +192,6 @@
     <t>Панин А</t>
   </si>
   <si>
-    <t>пятница</t>
-  </si>
-  <si>
     <t>Борщ</t>
   </si>
   <si>
@@ -228,9 +225,6 @@
     <t>×</t>
   </si>
   <si>
-    <t>четверг</t>
-  </si>
-  <si>
     <t>Суп харчо</t>
   </si>
   <si>
@@ -244,12 +238,6 @@
   </si>
   <si>
     <t>Волкова А</t>
-  </si>
-  <si>
-    <t>Рагулин С</t>
-  </si>
-  <si>
-    <t>Ковалев Б</t>
   </si>
   <si>
     <t>Общее кол-во
@@ -310,12 +298,6 @@
     <t>Чай</t>
   </si>
   <si>
-    <t>График дежурств отъезд 16 октября 2025г</t>
-  </si>
-  <si>
-    <t>отъезд 16 октября 2025г</t>
-  </si>
-  <si>
     <t>Каша с молоком или макароны</t>
   </si>
   <si>
@@ -335,6 +317,18 @@
   </si>
   <si>
     <t>Мкароны(сыр)</t>
+  </si>
+  <si>
+    <t>понедельник</t>
+  </si>
+  <si>
+    <t>вторник</t>
+  </si>
+  <si>
+    <t>отъезд 22 августа 2026г</t>
+  </si>
+  <si>
+    <t>График дежурств отъезд 22 августа 2026г</t>
   </si>
 </sst>
 </file>
@@ -1253,18 +1247,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1272,49 +1254,61 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1644,25 +1638,25 @@
   <sheetData>
     <row r="1" spans="1:33" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C2" s="130">
         <v>1</v>
       </c>
-      <c r="D2" s="139" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="140"/>
-      <c r="F2" s="140"/>
-      <c r="G2" s="140"/>
-      <c r="H2" s="140"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="140"/>
+      <c r="D2" s="159" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="51"/>
@@ -1673,9 +1667,9 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="141"/>
-      <c r="H3" s="141"/>
+      <c r="F3" s="161"/>
+      <c r="G3" s="161"/>
+      <c r="H3" s="161"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -1705,26 +1699,26 @@
     </row>
     <row r="5" spans="1:33" ht="56.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="131" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C5" s="131" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D5" s="129" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E5" s="48"/>
       <c r="F5" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="55" t="s">
-        <v>28</v>
-      </c>
       <c r="H5" s="55" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="I5" s="55" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="J5" s="55"/>
       <c r="K5" s="55"/>
@@ -1750,27 +1744,27 @@
     <row r="6" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="52">
         <f>COUNT(D8:D111)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="62">
         <f>B6/D6</f>
-        <v>2.2000000000000002</v>
+        <v>3.3333333333333335</v>
       </c>
       <c r="D6" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6" s="48"/>
       <c r="F6" s="55">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G6" s="56">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H6" s="55">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I6" s="56">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J6" s="55"/>
       <c r="K6" s="56"/>
@@ -1810,25 +1804,21 @@
       <c r="N7" s="51"/>
     </row>
     <row r="8" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="153">
+      <c r="A8" s="162">
         <v>5</v>
       </c>
       <c r="B8" s="57" t="str">
         <f>F5</f>
-        <v>четверг</v>
+        <v>суббота</v>
       </c>
       <c r="C8" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="65">
-        <v>5</v>
-      </c>
+      <c r="D8" s="65"/>
       <c r="E8" s="134" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="88" t="s">
-        <v>27</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="F8" s="88"/>
       <c r="G8" s="87"/>
       <c r="H8" s="64"/>
       <c r="I8" s="65"/>
@@ -1857,19 +1847,19 @@
       <c r="AG8" s="51"/>
     </row>
     <row r="9" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="138"/>
+      <c r="A9" s="158"/>
       <c r="B9" s="58">
         <f>F6</f>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C9" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D9" s="65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E9" s="69" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F9" s="73" t="s">
         <v>19</v>
@@ -1901,19 +1891,19 @@
       <c r="AE9" s="26"/>
     </row>
     <row r="10" spans="1:33" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="138"/>
+      <c r="A10" s="158"/>
       <c r="B10" s="59"/>
       <c r="C10" s="93" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D10" s="107">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E10" s="135" t="s">
         <v>16</v>
       </c>
       <c r="F10" s="74" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G10" s="94"/>
       <c r="H10" s="95"/>
@@ -1942,23 +1932,23 @@
       <c r="AE10" s="26"/>
     </row>
     <row r="11" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="138"/>
+      <c r="A11" s="158"/>
       <c r="B11" s="58" t="str">
         <f>G5</f>
-        <v>пятница</v>
+        <v>воскресенье</v>
       </c>
       <c r="C11" s="58" t="s">
         <v>22</v>
       </c>
       <c r="D11" s="126">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E11" s="132" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F11" s="78"/>
       <c r="G11" s="88" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H11" s="89"/>
       <c r="I11" s="90"/>
@@ -1986,23 +1976,23 @@
       <c r="AE11" s="26"/>
     </row>
     <row r="12" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="138"/>
+      <c r="A12" s="158"/>
       <c r="B12" s="58">
         <f>G6</f>
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D12" s="127">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E12" s="69" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F12" s="71"/>
       <c r="G12" s="73" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="H12" s="72"/>
       <c r="I12" s="70"/>
@@ -2030,20 +2020,20 @@
       <c r="AE12" s="26"/>
     </row>
     <row r="13" spans="1:33" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="138"/>
+      <c r="A13" s="158"/>
       <c r="B13" s="59"/>
       <c r="C13" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D13" s="127">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E13" s="133" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F13" s="102"/>
       <c r="G13" s="74" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="H13" s="103"/>
       <c r="I13" s="96"/>
@@ -2071,19 +2061,19 @@
       <c r="AE13" s="26"/>
     </row>
     <row r="14" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="138"/>
+      <c r="A14" s="158"/>
       <c r="B14" s="58" t="str">
         <f>H5</f>
-        <v>суббота</v>
+        <v>понедельник</v>
       </c>
       <c r="C14" s="58" t="s">
         <v>22</v>
       </c>
       <c r="D14" s="127">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E14" s="134" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F14" s="90"/>
       <c r="G14" s="75"/>
@@ -2115,24 +2105,24 @@
       <c r="AE14" s="26"/>
     </row>
     <row r="15" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="138"/>
+      <c r="A15" s="158"/>
       <c r="B15" s="58">
         <f>H6</f>
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C15" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D15" s="127">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E15" s="69" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F15" s="70"/>
       <c r="G15" s="76"/>
       <c r="H15" s="73" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="I15" s="77"/>
       <c r="J15" s="65"/>
@@ -2159,21 +2149,21 @@
       <c r="AE15" s="26"/>
     </row>
     <row r="16" spans="1:33" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="138"/>
+      <c r="A16" s="158"/>
       <c r="B16" s="59"/>
       <c r="C16" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D16" s="127">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E16" s="135" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F16" s="96"/>
       <c r="G16" s="105"/>
       <c r="H16" s="74" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I16" s="106"/>
       <c r="J16" s="107"/>
@@ -2200,25 +2190,25 @@
       <c r="AE16" s="26"/>
     </row>
     <row r="17" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="138"/>
+      <c r="A17" s="158"/>
       <c r="B17" s="58" t="str">
         <f>I5</f>
-        <v>воскресенье</v>
+        <v>вторник</v>
       </c>
       <c r="C17" s="58" t="s">
         <v>22</v>
       </c>
       <c r="D17" s="127">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E17" s="132" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F17" s="90"/>
       <c r="G17" s="90"/>
       <c r="H17" s="78"/>
       <c r="I17" s="88" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="J17" s="104"/>
       <c r="K17" s="92"/>
@@ -2244,19 +2234,19 @@
       <c r="AE17" s="26"/>
     </row>
     <row r="18" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="138"/>
+      <c r="A18" s="158"/>
       <c r="B18" s="58">
         <f>I6</f>
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D18" s="127">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E18" s="69" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F18" s="68"/>
       <c r="G18" s="68"/>
@@ -2288,10 +2278,10 @@
       <c r="AE18" s="26"/>
     </row>
     <row r="19" spans="1:33" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="138"/>
+      <c r="A19" s="158"/>
       <c r="B19" s="59"/>
       <c r="C19" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D19" s="127"/>
       <c r="E19" s="133"/>
@@ -2323,7 +2313,7 @@
       <c r="AE19" s="26"/>
     </row>
     <row r="20" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="138"/>
+      <c r="A20" s="158"/>
       <c r="B20" s="58">
         <f>J5</f>
         <v>0</v>
@@ -2361,13 +2351,13 @@
       <c r="AE20" s="26"/>
     </row>
     <row r="21" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="138"/>
+      <c r="A21" s="158"/>
       <c r="B21" s="58">
         <f>J6</f>
         <v>0</v>
       </c>
       <c r="C21" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D21" s="127"/>
       <c r="E21" s="69"/>
@@ -2399,10 +2389,10 @@
       <c r="AE21" s="26"/>
     </row>
     <row r="22" spans="1:33" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="138"/>
+      <c r="A22" s="158"/>
       <c r="B22" s="59"/>
       <c r="C22" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D22" s="127"/>
       <c r="E22" s="135"/>
@@ -2434,7 +2424,7 @@
       <c r="AE22" s="26"/>
     </row>
     <row r="23" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="138"/>
+      <c r="A23" s="158"/>
       <c r="B23" s="58">
         <f>K5</f>
         <v>0</v>
@@ -2472,13 +2462,13 @@
       <c r="AE23" s="26"/>
     </row>
     <row r="24" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="138"/>
+      <c r="A24" s="158"/>
       <c r="B24" s="58">
         <f>K6</f>
         <v>0</v>
       </c>
       <c r="C24" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D24" s="127"/>
       <c r="E24" s="69"/>
@@ -2510,10 +2500,10 @@
       <c r="AE24" s="26"/>
     </row>
     <row r="25" spans="1:33" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="138"/>
+      <c r="A25" s="158"/>
       <c r="B25" s="59"/>
       <c r="C25" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D25" s="107"/>
       <c r="E25" s="133"/>
@@ -2545,7 +2535,7 @@
       <c r="AE25" s="26"/>
     </row>
     <row r="26" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="138"/>
+      <c r="A26" s="158"/>
       <c r="B26" s="58">
         <f>L5</f>
         <v>0</v>
@@ -2583,13 +2573,13 @@
       <c r="AE26" s="36"/>
     </row>
     <row r="27" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="138"/>
+      <c r="A27" s="158"/>
       <c r="B27" s="58">
         <f>L6</f>
         <v>0</v>
       </c>
       <c r="C27" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D27" s="65"/>
       <c r="E27" s="69"/>
@@ -2621,10 +2611,10 @@
       <c r="AE27" s="36"/>
     </row>
     <row r="28" spans="1:33" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="138"/>
+      <c r="A28" s="158"/>
       <c r="B28" s="59"/>
       <c r="C28" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D28" s="107"/>
       <c r="E28" s="135"/>
@@ -2656,7 +2646,7 @@
       <c r="AE28" s="36"/>
     </row>
     <row r="29" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="138">
+      <c r="A29" s="158">
         <v>4</v>
       </c>
       <c r="B29" s="58">
@@ -2697,13 +2687,13 @@
       <c r="AF29" s="36"/>
     </row>
     <row r="30" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="138"/>
+      <c r="A30" s="158"/>
       <c r="B30" s="58">
         <f>M6</f>
         <v>0</v>
       </c>
       <c r="C30" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D30" s="127"/>
       <c r="E30" s="69"/>
@@ -2736,10 +2726,10 @@
       <c r="AF30" s="36"/>
     </row>
     <row r="31" spans="1:33" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="138"/>
+      <c r="A31" s="158"/>
       <c r="B31" s="59"/>
       <c r="C31" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D31" s="128"/>
       <c r="E31" s="136"/>
@@ -2772,7 +2762,7 @@
       <c r="AF31" s="36"/>
     </row>
     <row r="32" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="138"/>
+      <c r="A32" s="158"/>
       <c r="B32" s="58">
         <f>N5</f>
         <v>0</v>
@@ -2811,13 +2801,13 @@
       <c r="AG32" s="36"/>
     </row>
     <row r="33" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="138"/>
+      <c r="A33" s="158"/>
       <c r="B33" s="58">
         <f>N6</f>
         <v>0</v>
       </c>
       <c r="C33" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D33" s="127"/>
       <c r="E33" s="69"/>
@@ -2850,10 +2840,10 @@
       <c r="AG33" s="36"/>
     </row>
     <row r="34" spans="1:33" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="138"/>
+      <c r="A34" s="158"/>
       <c r="B34" s="59"/>
       <c r="C34" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D34" s="128"/>
       <c r="E34" s="135"/>
@@ -2883,7 +2873,7 @@
       <c r="AC34" s="97"/>
     </row>
     <row r="35" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="138"/>
+      <c r="A35" s="158"/>
       <c r="B35" s="58">
         <f>O5</f>
         <v>0</v>
@@ -2919,13 +2909,13 @@
       <c r="AC35" s="67"/>
     </row>
     <row r="36" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="138"/>
+      <c r="A36" s="158"/>
       <c r="B36" s="58">
         <f>O6</f>
         <v>0</v>
       </c>
       <c r="C36" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D36" s="127"/>
       <c r="E36" s="69"/>
@@ -2955,10 +2945,10 @@
       <c r="AC36" s="67"/>
     </row>
     <row r="37" spans="1:33" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="138"/>
+      <c r="A37" s="158"/>
       <c r="B37" s="59"/>
       <c r="C37" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D37" s="128"/>
       <c r="E37" s="136"/>
@@ -2988,7 +2978,7 @@
       <c r="AC37" s="97"/>
     </row>
     <row r="38" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="138"/>
+      <c r="A38" s="158"/>
       <c r="B38" s="58">
         <f>P5</f>
         <v>0</v>
@@ -3024,13 +3014,13 @@
       <c r="AC38" s="67"/>
     </row>
     <row r="39" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="138"/>
+      <c r="A39" s="158"/>
       <c r="B39" s="58">
         <f>P6</f>
         <v>0</v>
       </c>
       <c r="C39" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D39" s="127"/>
       <c r="E39" s="69"/>
@@ -3060,10 +3050,10 @@
       <c r="AC39" s="67"/>
     </row>
     <row r="40" spans="1:33" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="138"/>
+      <c r="A40" s="158"/>
       <c r="B40" s="59"/>
       <c r="C40" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D40" s="128"/>
       <c r="E40" s="135"/>
@@ -3093,7 +3083,7 @@
       <c r="AC40" s="97"/>
     </row>
     <row r="41" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="138"/>
+      <c r="A41" s="158"/>
       <c r="B41" s="58">
         <f>Q5</f>
         <v>0</v>
@@ -3129,13 +3119,13 @@
       <c r="AC41" s="67"/>
     </row>
     <row r="42" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="138"/>
+      <c r="A42" s="158"/>
       <c r="B42" s="58">
         <f>Q6</f>
         <v>0</v>
       </c>
       <c r="C42" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D42" s="127"/>
       <c r="E42" s="69"/>
@@ -3165,10 +3155,10 @@
       <c r="AC42" s="67"/>
     </row>
     <row r="43" spans="1:33" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="138"/>
+      <c r="A43" s="158"/>
       <c r="B43" s="59"/>
       <c r="C43" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D43" s="128"/>
       <c r="E43" s="136"/>
@@ -3198,7 +3188,7 @@
       <c r="AC43" s="97"/>
     </row>
     <row r="44" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="138"/>
+      <c r="A44" s="158"/>
       <c r="B44" s="58">
         <f>R5</f>
         <v>0</v>
@@ -3234,13 +3224,13 @@
       <c r="AC44" s="67"/>
     </row>
     <row r="45" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="138"/>
+      <c r="A45" s="158"/>
       <c r="B45" s="58">
         <f>R6</f>
         <v>0</v>
       </c>
       <c r="C45" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D45" s="127"/>
       <c r="E45" s="69"/>
@@ -3270,10 +3260,10 @@
       <c r="AC45" s="67"/>
     </row>
     <row r="46" spans="1:33" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="138"/>
+      <c r="A46" s="158"/>
       <c r="B46" s="59"/>
       <c r="C46" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D46" s="128"/>
       <c r="E46" s="135"/>
@@ -3303,7 +3293,7 @@
       <c r="AC46" s="97"/>
     </row>
     <row r="47" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="138"/>
+      <c r="A47" s="158"/>
       <c r="B47" s="58">
         <f>S5</f>
         <v>0</v>
@@ -3339,13 +3329,13 @@
       <c r="AC47" s="67"/>
     </row>
     <row r="48" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="138"/>
+      <c r="A48" s="158"/>
       <c r="B48" s="58">
         <f>S6</f>
         <v>0</v>
       </c>
       <c r="C48" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D48" s="127"/>
       <c r="E48" s="69"/>
@@ -3375,10 +3365,10 @@
       <c r="AC48" s="67"/>
     </row>
     <row r="49" spans="1:29" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="138"/>
+      <c r="A49" s="158"/>
       <c r="B49" s="59"/>
       <c r="C49" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D49" s="128"/>
       <c r="E49" s="136"/>
@@ -3408,7 +3398,7 @@
       <c r="AC49" s="97"/>
     </row>
     <row r="50" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="138"/>
+      <c r="A50" s="158"/>
       <c r="B50" s="58">
         <f>T5</f>
         <v>0</v>
@@ -3444,13 +3434,13 @@
       <c r="AC50" s="67"/>
     </row>
     <row r="51" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="138"/>
+      <c r="A51" s="158"/>
       <c r="B51" s="58">
         <f>T6</f>
         <v>0</v>
       </c>
       <c r="C51" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D51" s="127"/>
       <c r="E51" s="69"/>
@@ -3480,10 +3470,10 @@
       <c r="AC51" s="67"/>
     </row>
     <row r="52" spans="1:29" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="138"/>
+      <c r="A52" s="158"/>
       <c r="B52" s="59"/>
       <c r="C52" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D52" s="128"/>
       <c r="E52" s="135"/>
@@ -3513,7 +3503,7 @@
       <c r="AC52" s="97"/>
     </row>
     <row r="53" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="138"/>
+      <c r="A53" s="158"/>
       <c r="B53" s="58">
         <f>U5</f>
         <v>0</v>
@@ -3549,13 +3539,13 @@
       <c r="AC53" s="67"/>
     </row>
     <row r="54" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="138"/>
+      <c r="A54" s="158"/>
       <c r="B54" s="58">
         <f>U6</f>
         <v>0</v>
       </c>
       <c r="C54" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D54" s="127"/>
       <c r="E54" s="69"/>
@@ -3585,10 +3575,10 @@
       <c r="AC54" s="67"/>
     </row>
     <row r="55" spans="1:29" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="138"/>
+      <c r="A55" s="158"/>
       <c r="B55" s="59"/>
       <c r="C55" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D55" s="128"/>
       <c r="E55" s="136"/>
@@ -3618,7 +3608,7 @@
       <c r="AC55" s="97"/>
     </row>
     <row r="56" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="138"/>
+      <c r="A56" s="158"/>
       <c r="B56" s="58">
         <f>V5</f>
         <v>0</v>
@@ -3654,13 +3644,13 @@
       <c r="AC56" s="67"/>
     </row>
     <row r="57" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="138"/>
+      <c r="A57" s="158"/>
       <c r="B57" s="58">
         <f>V6</f>
         <v>0</v>
       </c>
       <c r="C57" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D57" s="127"/>
       <c r="E57" s="69"/>
@@ -3690,10 +3680,10 @@
       <c r="AC57" s="67"/>
     </row>
     <row r="58" spans="1:29" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="138"/>
+      <c r="A58" s="158"/>
       <c r="B58" s="59"/>
       <c r="C58" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D58" s="128"/>
       <c r="E58" s="135"/>
@@ -3723,7 +3713,7 @@
       <c r="AC58" s="97"/>
     </row>
     <row r="59" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="138"/>
+      <c r="A59" s="158"/>
       <c r="B59" s="58">
         <f>W5</f>
         <v>0</v>
@@ -3759,13 +3749,13 @@
       <c r="AC59" s="67"/>
     </row>
     <row r="60" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="138"/>
+      <c r="A60" s="158"/>
       <c r="B60" s="58">
         <f>W6</f>
         <v>0</v>
       </c>
       <c r="C60" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D60" s="127"/>
       <c r="E60" s="69"/>
@@ -3795,10 +3785,10 @@
       <c r="AC60" s="67"/>
     </row>
     <row r="61" spans="1:29" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="138"/>
+      <c r="A61" s="158"/>
       <c r="B61" s="59"/>
       <c r="C61" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D61" s="128"/>
       <c r="E61" s="136"/>
@@ -3828,7 +3818,7 @@
       <c r="AC61" s="97"/>
     </row>
     <row r="62" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="138"/>
+      <c r="A62" s="158"/>
       <c r="B62" s="58">
         <f>X5</f>
         <v>0</v>
@@ -3864,13 +3854,13 @@
       <c r="AC62" s="67"/>
     </row>
     <row r="63" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="138"/>
+      <c r="A63" s="158"/>
       <c r="B63" s="58">
         <f>X6</f>
         <v>0</v>
       </c>
       <c r="C63" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D63" s="127"/>
       <c r="E63" s="69"/>
@@ -3900,10 +3890,10 @@
       <c r="AC63" s="67"/>
     </row>
     <row r="64" spans="1:29" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="138"/>
+      <c r="A64" s="158"/>
       <c r="B64" s="59"/>
       <c r="C64" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D64" s="128"/>
       <c r="E64" s="135"/>
@@ -3933,7 +3923,7 @@
       <c r="AC64" s="97"/>
     </row>
     <row r="65" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="138"/>
+      <c r="A65" s="158"/>
       <c r="B65" s="58">
         <f>Y5</f>
         <v>0</v>
@@ -3969,13 +3959,13 @@
       <c r="AC65" s="67"/>
     </row>
     <row r="66" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="138"/>
+      <c r="A66" s="158"/>
       <c r="B66" s="58">
         <f>Y6</f>
         <v>0</v>
       </c>
       <c r="C66" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D66" s="127"/>
       <c r="E66" s="69"/>
@@ -4005,10 +3995,10 @@
       <c r="AC66" s="67"/>
     </row>
     <row r="67" spans="1:29" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="138"/>
+      <c r="A67" s="158"/>
       <c r="B67" s="59"/>
       <c r="C67" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D67" s="128"/>
       <c r="E67" s="136"/>
@@ -4038,7 +4028,7 @@
       <c r="AC67" s="97"/>
     </row>
     <row r="68" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="138"/>
+      <c r="A68" s="158"/>
       <c r="B68" s="58">
         <f>Z5</f>
         <v>0</v>
@@ -4074,13 +4064,13 @@
       <c r="AC68" s="67"/>
     </row>
     <row r="69" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="138"/>
+      <c r="A69" s="158"/>
       <c r="B69" s="58">
         <f>Z6</f>
         <v>0</v>
       </c>
       <c r="C69" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D69" s="127"/>
       <c r="E69" s="69"/>
@@ -4110,10 +4100,10 @@
       <c r="AC69" s="67"/>
     </row>
     <row r="70" spans="1:29" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="138"/>
+      <c r="A70" s="158"/>
       <c r="B70" s="59"/>
       <c r="C70" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D70" s="128"/>
       <c r="E70" s="135"/>
@@ -4143,7 +4133,7 @@
       <c r="AC70" s="97"/>
     </row>
     <row r="71" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="138"/>
+      <c r="A71" s="158"/>
       <c r="B71" s="58">
         <f>AA5</f>
         <v>0</v>
@@ -4179,13 +4169,13 @@
       <c r="AC71" s="67"/>
     </row>
     <row r="72" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="138"/>
+      <c r="A72" s="158"/>
       <c r="B72" s="58">
         <f>AA6</f>
         <v>0</v>
       </c>
       <c r="C72" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D72" s="127"/>
       <c r="E72" s="69"/>
@@ -4215,10 +4205,10 @@
       <c r="AC72" s="67"/>
     </row>
     <row r="73" spans="1:29" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="138"/>
+      <c r="A73" s="158"/>
       <c r="B73" s="59"/>
       <c r="C73" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D73" s="128"/>
       <c r="E73" s="136"/>
@@ -4248,7 +4238,7 @@
       <c r="AC73" s="97"/>
     </row>
     <row r="74" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="138"/>
+      <c r="A74" s="158"/>
       <c r="B74" s="58">
         <f>AB5</f>
         <v>0</v>
@@ -4284,13 +4274,13 @@
       <c r="AC74" s="67"/>
     </row>
     <row r="75" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="138"/>
+      <c r="A75" s="158"/>
       <c r="B75" s="58">
         <f>AB6</f>
         <v>0</v>
       </c>
       <c r="C75" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D75" s="127"/>
       <c r="E75" s="69"/>
@@ -4320,10 +4310,10 @@
       <c r="AC75" s="67"/>
     </row>
     <row r="76" spans="1:29" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="138"/>
+      <c r="A76" s="158"/>
       <c r="B76" s="59"/>
       <c r="C76" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D76" s="128"/>
       <c r="E76" s="135"/>
@@ -4353,7 +4343,7 @@
       <c r="AC76" s="115"/>
     </row>
     <row r="77" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="138"/>
+      <c r="A77" s="158"/>
       <c r="B77" s="58">
         <f>AC5</f>
         <v>0</v>
@@ -4394,7 +4384,7 @@
         <v>0</v>
       </c>
       <c r="C78" s="58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D78" s="127"/>
       <c r="E78" s="69"/>
@@ -4426,7 +4416,7 @@
     <row r="79" spans="1:29" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" s="59"/>
       <c r="C79" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D79" s="128"/>
       <c r="E79" s="110"/>
@@ -4576,14 +4566,14 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="46" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E2" s="46"/>
       <c r="F2" s="46"/>
       <c r="G2" s="46"/>
       <c r="H2" s="22"/>
       <c r="I2" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J2" s="22"/>
       <c r="K2" s="23"/>
@@ -4593,7 +4583,7 @@
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
       <c r="Q2" s="52" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="R2" s="130">
         <f>График!C2</f>
@@ -4718,31 +4708,31 @@
       <c r="CP4" s="51"/>
     </row>
     <row r="5" spans="1:94" ht="35.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="150" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="150"/>
-      <c r="D5" s="150"/>
-      <c r="E5" s="150"/>
-      <c r="F5" s="150"/>
-      <c r="G5" s="150"/>
-      <c r="H5" s="150"/>
-      <c r="I5" s="152"/>
+      <c r="B5" s="147" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="147"/>
+      <c r="D5" s="147"/>
+      <c r="E5" s="147"/>
+      <c r="F5" s="147"/>
+      <c r="G5" s="147"/>
+      <c r="H5" s="147"/>
+      <c r="I5" s="148"/>
       <c r="J5" s="20">
         <v>1</v>
       </c>
-      <c r="K5" s="151" t="s">
-        <v>62</v>
-      </c>
-      <c r="L5" s="143"/>
-      <c r="M5" s="143"/>
-      <c r="N5" s="143"/>
-      <c r="O5" s="142" t="s">
-        <v>68</v>
-      </c>
-      <c r="P5" s="142"/>
-      <c r="Q5" s="142"/>
-      <c r="R5" s="142"/>
+      <c r="K5" s="146" t="s">
+        <v>58</v>
+      </c>
+      <c r="L5" s="139"/>
+      <c r="M5" s="139"/>
+      <c r="N5" s="139"/>
+      <c r="O5" s="138" t="s">
+        <v>72</v>
+      </c>
+      <c r="P5" s="138"/>
+      <c r="Q5" s="138"/>
+      <c r="R5" s="138"/>
       <c r="S5" s="17"/>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
@@ -4926,11 +4916,11 @@
       </c>
       <c r="H7" s="51"/>
       <c r="I7" s="51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J7" s="51"/>
       <c r="K7" s="51" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="L7" s="51"/>
       <c r="M7" s="51"/>
@@ -5020,10 +5010,10 @@
       <c r="B8" s="10">
         <v>1</v>
       </c>
-      <c r="C8" s="154" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" s="154"/>
+      <c r="C8" s="149" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="149"/>
       <c r="E8" s="12">
         <f>SUM(G8,I8,K8)</f>
         <v>0</v>
@@ -5132,8 +5122,8 @@
     </row>
     <row r="9" spans="1:94" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B9" s="54"/>
-      <c r="C9" s="154"/>
-      <c r="D9" s="154"/>
+      <c r="C9" s="149"/>
+      <c r="D9" s="149"/>
       <c r="E9" s="12"/>
       <c r="F9" s="53"/>
       <c r="G9" s="38"/>
@@ -5274,18 +5264,18 @@
       <c r="B11" s="54">
         <v>2</v>
       </c>
-      <c r="C11" s="143" t="s">
+      <c r="C11" s="139" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="143"/>
+      <c r="D11" s="139"/>
       <c r="E11" s="37"/>
-      <c r="F11" s="143" t="s">
+      <c r="F11" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="143"/>
-      <c r="H11" s="143"/>
-      <c r="I11" s="143"/>
-      <c r="J11" s="143"/>
+      <c r="G11" s="139"/>
+      <c r="H11" s="139"/>
+      <c r="I11" s="139"/>
+      <c r="J11" s="139"/>
       <c r="K11" s="51"/>
       <c r="L11" s="51"/>
       <c r="M11" s="51"/>
@@ -5373,19 +5363,19 @@
       <c r="E13" s="12"/>
       <c r="F13" s="51"/>
       <c r="G13" s="43" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H13" s="51"/>
       <c r="I13" s="43" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J13" s="51"/>
       <c r="K13" s="51" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="L13" s="51"/>
       <c r="M13" s="51" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N13" s="51"/>
       <c r="O13" s="51"/>
@@ -5423,10 +5413,10 @@
       <c r="B14" s="49">
         <v>3</v>
       </c>
-      <c r="C14" s="144" t="s">
+      <c r="C14" s="140" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="144"/>
+      <c r="D14" s="140"/>
       <c r="E14" s="12">
         <f>SUM(G14,I14,K14,M14)</f>
         <v>0</v>
@@ -5581,18 +5571,18 @@
       <c r="B17" s="54">
         <v>4</v>
       </c>
-      <c r="C17" s="143" t="s">
+      <c r="C17" s="139" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="143"/>
+      <c r="D17" s="139"/>
       <c r="E17" s="37"/>
-      <c r="F17" s="143" t="s">
+      <c r="F17" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="G17" s="143"/>
-      <c r="H17" s="143"/>
-      <c r="I17" s="143"/>
-      <c r="J17" s="143"/>
+      <c r="G17" s="139"/>
+      <c r="H17" s="139"/>
+      <c r="I17" s="139"/>
+      <c r="J17" s="139"/>
       <c r="K17" s="51"/>
       <c r="L17" s="51"/>
       <c r="M17" s="51"/>
@@ -5680,15 +5670,15 @@
       <c r="E19" s="12"/>
       <c r="F19" s="51"/>
       <c r="G19" s="43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H19" s="51"/>
       <c r="I19" s="43" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J19" s="51"/>
       <c r="K19" s="51" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="L19" s="51"/>
       <c r="M19" s="51" t="s">
@@ -5730,10 +5720,10 @@
       <c r="B20" s="24">
         <v>5</v>
       </c>
-      <c r="C20" s="147" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" s="147"/>
+      <c r="C20" s="150" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="150"/>
       <c r="E20" s="12">
         <f>SUM(G20,I20,K20)</f>
         <v>0</v>
@@ -5843,7 +5833,7 @@
     <row r="22" spans="2:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="54"/>
       <c r="C22" s="51" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D22" s="51"/>
       <c r="E22" s="12">
@@ -5853,14 +5843,14 @@
       <c r="F22" s="53"/>
       <c r="G22" s="12"/>
       <c r="H22" s="53"/>
-      <c r="I22" s="148" t="s">
+      <c r="I22" s="144" t="s">
         <v>24</v>
       </c>
-      <c r="J22" s="148"/>
-      <c r="K22" s="149" t="s">
-        <v>59</v>
-      </c>
-      <c r="L22" s="149"/>
+      <c r="J22" s="144"/>
+      <c r="K22" s="145" t="s">
+        <v>55</v>
+      </c>
+      <c r="L22" s="145"/>
       <c r="M22" s="51"/>
       <c r="N22" s="51"/>
       <c r="O22" s="51"/>
@@ -5902,15 +5892,15 @@
       <c r="F23" s="51"/>
       <c r="G23" s="51"/>
       <c r="H23" s="2"/>
-      <c r="I23" s="148" t="s">
-        <v>58</v>
-      </c>
-      <c r="J23" s="148"/>
-      <c r="K23" s="148" t="s">
-        <v>60</v>
-      </c>
-      <c r="L23" s="148"/>
-      <c r="M23" s="148"/>
+      <c r="I23" s="144" t="s">
+        <v>54</v>
+      </c>
+      <c r="J23" s="144"/>
+      <c r="K23" s="144" t="s">
+        <v>56</v>
+      </c>
+      <c r="L23" s="144"/>
+      <c r="M23" s="144"/>
       <c r="N23" s="51"/>
       <c r="O23" s="51"/>
       <c r="P23" s="51"/>
@@ -5953,17 +5943,17 @@
       <c r="H24" s="51"/>
       <c r="I24" s="53"/>
       <c r="J24" s="51"/>
-      <c r="K24" s="149"/>
-      <c r="L24" s="149"/>
+      <c r="K24" s="145"/>
+      <c r="L24" s="145"/>
       <c r="M24" s="51"/>
       <c r="N24" s="51"/>
       <c r="O24" s="51"/>
       <c r="P24" s="51"/>
-      <c r="Q24" s="143" t="s">
+      <c r="Q24" s="139" t="s">
         <v>5</v>
       </c>
-      <c r="R24" s="143"/>
-      <c r="S24" s="143"/>
+      <c r="R24" s="139"/>
+      <c r="S24" s="139"/>
       <c r="T24" s="51" t="s">
         <v>2</v>
       </c>
@@ -6091,23 +6081,23 @@
       <c r="C27" s="9">
         <v>1</v>
       </c>
-      <c r="D27" s="146" t="s">
-        <v>30</v>
-      </c>
-      <c r="E27" s="146"/>
-      <c r="F27" s="146"/>
+      <c r="D27" s="142" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" s="142"/>
+      <c r="F27" s="142"/>
       <c r="G27" s="12">
         <v>90</v>
       </c>
       <c r="H27" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I27" s="28">
         <f>G20</f>
         <v>0</v>
       </c>
       <c r="J27" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K27" s="12">
         <f>J5</f>
@@ -6160,23 +6150,23 @@
       <c r="C28" s="9">
         <v>2</v>
       </c>
-      <c r="D28" s="145" t="s">
-        <v>38</v>
-      </c>
-      <c r="E28" s="145"/>
-      <c r="F28" s="145"/>
+      <c r="D28" s="141" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="141"/>
+      <c r="F28" s="141"/>
       <c r="G28" s="12">
         <v>90</v>
       </c>
       <c r="H28" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I28" s="45">
         <f>I20</f>
         <v>0</v>
       </c>
       <c r="J28" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K28" s="12">
         <f>J5</f>
@@ -6238,14 +6228,14 @@
         <v>0</v>
       </c>
       <c r="H29" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I29" s="29">
         <f>M20</f>
         <v>0</v>
       </c>
       <c r="J29" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K29" s="12">
         <f>J5</f>
@@ -6298,23 +6288,23 @@
       <c r="C30" s="9">
         <v>4</v>
       </c>
-      <c r="D30" s="161" t="s">
-        <v>72</v>
-      </c>
-      <c r="E30" s="162"/>
-      <c r="F30" s="162"/>
+      <c r="D30" s="156" t="s">
+        <v>66</v>
+      </c>
+      <c r="E30" s="157"/>
+      <c r="F30" s="157"/>
       <c r="G30" s="12">
         <v>90</v>
       </c>
       <c r="H30" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I30" s="29">
         <f>K20</f>
         <v>0</v>
       </c>
       <c r="J30" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K30" s="12">
         <f>J5</f>
@@ -6367,23 +6357,23 @@
       <c r="C31" s="9">
         <v>5</v>
       </c>
-      <c r="D31" s="143" t="s">
-        <v>37</v>
-      </c>
-      <c r="E31" s="143"/>
-      <c r="F31" s="143"/>
+      <c r="D31" s="139" t="s">
+        <v>36</v>
+      </c>
+      <c r="E31" s="139"/>
+      <c r="F31" s="139"/>
       <c r="G31" s="12">
         <v>100</v>
       </c>
       <c r="H31" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I31" s="12">
         <f>E20</f>
         <v>0</v>
       </c>
       <c r="J31" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K31" s="12">
         <f>J5</f>
@@ -6443,23 +6433,23 @@
       <c r="C32" s="9">
         <v>6</v>
       </c>
-      <c r="D32" s="143" t="s">
+      <c r="D32" s="139" t="s">
         <v>26</v>
       </c>
-      <c r="E32" s="143"/>
-      <c r="F32" s="143"/>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139"/>
       <c r="G32" s="12">
         <v>2</v>
       </c>
       <c r="H32" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I32" s="12">
         <f>E20</f>
         <v>0</v>
       </c>
       <c r="J32" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K32" s="12">
         <f>J5</f>
@@ -6509,11 +6499,11 @@
       <c r="C33" s="9">
         <v>7</v>
       </c>
-      <c r="D33" s="143" t="s">
-        <v>32</v>
-      </c>
-      <c r="E33" s="143"/>
-      <c r="F33" s="143"/>
+      <c r="D33" s="139" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" s="139"/>
+      <c r="F33" s="139"/>
       <c r="G33" s="12"/>
       <c r="H33" s="53"/>
       <c r="I33" s="12"/>
@@ -6602,10 +6592,10 @@
       <c r="B35" s="54">
         <v>2</v>
       </c>
-      <c r="C35" s="143" t="s">
+      <c r="C35" s="139" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="143"/>
+      <c r="D35" s="139"/>
       <c r="E35" s="51"/>
       <c r="F35" s="51"/>
       <c r="G35" s="51"/>
@@ -6695,18 +6685,18 @@
       <c r="B37" s="49">
         <v>3</v>
       </c>
-      <c r="C37" s="144" t="s">
+      <c r="C37" s="140" t="s">
         <v>12</v>
       </c>
-      <c r="D37" s="144"/>
+      <c r="D37" s="140"/>
       <c r="E37" s="51"/>
-      <c r="F37" s="143" t="s">
+      <c r="F37" s="139" t="s">
         <v>7</v>
       </c>
-      <c r="G37" s="143"/>
-      <c r="H37" s="143"/>
-      <c r="I37" s="143"/>
-      <c r="J37" s="143"/>
+      <c r="G37" s="139"/>
+      <c r="H37" s="139"/>
+      <c r="I37" s="139"/>
+      <c r="J37" s="139"/>
       <c r="K37" s="51"/>
       <c r="L37" s="51"/>
       <c r="M37" s="51"/>
@@ -6747,23 +6737,23 @@
       <c r="C38" s="9">
         <v>1</v>
       </c>
-      <c r="D38" s="143" t="s">
+      <c r="D38" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="E38" s="143"/>
-      <c r="F38" s="143"/>
+      <c r="E38" s="139"/>
+      <c r="F38" s="139"/>
       <c r="G38" s="12">
         <v>100</v>
       </c>
       <c r="H38" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I38" s="12">
         <f>E14</f>
         <v>0</v>
       </c>
       <c r="J38" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K38" s="12">
         <f>J5</f>
@@ -6816,23 +6806,23 @@
       <c r="C39" s="9">
         <v>2</v>
       </c>
-      <c r="D39" s="156" t="s">
-        <v>41</v>
-      </c>
-      <c r="E39" s="156"/>
-      <c r="F39" s="156"/>
+      <c r="D39" s="151" t="s">
+        <v>39</v>
+      </c>
+      <c r="E39" s="151"/>
+      <c r="F39" s="151"/>
       <c r="G39" s="18">
         <v>0.5</v>
       </c>
       <c r="H39" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I39" s="12">
         <f>G14</f>
         <v>0</v>
       </c>
       <c r="J39" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K39" s="12">
         <f>J5</f>
@@ -6882,23 +6872,23 @@
       <c r="C40" s="9">
         <v>3</v>
       </c>
-      <c r="D40" s="157" t="s">
-        <v>29</v>
-      </c>
-      <c r="E40" s="157"/>
-      <c r="F40" s="157"/>
+      <c r="D40" s="152" t="s">
+        <v>28</v>
+      </c>
+      <c r="E40" s="152"/>
+      <c r="F40" s="152"/>
       <c r="G40" s="18">
         <v>0.5</v>
       </c>
       <c r="H40" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I40" s="12">
         <f>I14</f>
         <v>0</v>
       </c>
       <c r="J40" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K40" s="12">
         <f>J5</f>
@@ -6926,23 +6916,23 @@
       <c r="C41" s="9">
         <v>4</v>
       </c>
-      <c r="D41" s="158" t="s">
-        <v>51</v>
-      </c>
-      <c r="E41" s="159"/>
-      <c r="F41" s="160"/>
+      <c r="D41" s="153" t="s">
+        <v>47</v>
+      </c>
+      <c r="E41" s="154"/>
+      <c r="F41" s="155"/>
       <c r="G41" s="18">
         <v>0.5</v>
       </c>
       <c r="H41" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I41" s="12">
         <f>K14</f>
         <v>0</v>
       </c>
       <c r="J41" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K41" s="12">
         <f>J5</f>
@@ -6970,23 +6960,23 @@
       <c r="C42" s="9">
         <v>5</v>
       </c>
-      <c r="D42" s="143" t="s">
+      <c r="D42" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="143"/>
-      <c r="F42" s="143"/>
+      <c r="E42" s="139"/>
+      <c r="F42" s="139"/>
       <c r="G42" s="12">
         <v>2</v>
       </c>
       <c r="H42" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I42" s="12">
         <f>E14</f>
         <v>0</v>
       </c>
       <c r="J42" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K42" s="12">
         <f>J5</f>
@@ -7017,23 +7007,23 @@
       <c r="C43" s="9">
         <v>6</v>
       </c>
-      <c r="D43" s="143" t="s">
+      <c r="D43" s="139" t="s">
         <v>8</v>
       </c>
-      <c r="E43" s="143"/>
-      <c r="F43" s="143"/>
+      <c r="E43" s="139"/>
+      <c r="F43" s="139"/>
       <c r="G43" s="14">
         <v>0.25</v>
       </c>
       <c r="H43" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I43" s="12">
         <f>E14</f>
         <v>0</v>
       </c>
       <c r="J43" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K43" s="12">
         <f>J5</f>
@@ -7066,11 +7056,11 @@
       <c r="C44" s="9">
         <v>7</v>
       </c>
-      <c r="D44" s="143" t="s">
-        <v>32</v>
-      </c>
-      <c r="E44" s="143"/>
-      <c r="F44" s="143"/>
+      <c r="D44" s="139" t="s">
+        <v>31</v>
+      </c>
+      <c r="E44" s="139"/>
+      <c r="F44" s="139"/>
       <c r="G44" s="51"/>
       <c r="H44" s="51"/>
       <c r="I44" s="51"/>
@@ -7094,7 +7084,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="51" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E45" s="51"/>
       <c r="F45" s="51"/>
@@ -7119,10 +7109,10 @@
       <c r="B46" s="54">
         <v>4</v>
       </c>
-      <c r="C46" s="143" t="s">
+      <c r="C46" s="139" t="s">
         <v>13</v>
       </c>
-      <c r="D46" s="143"/>
+      <c r="D46" s="139"/>
       <c r="E46" s="51"/>
       <c r="F46" s="51"/>
       <c r="G46" s="51"/>
@@ -7169,10 +7159,10 @@
       <c r="B48" s="19">
         <v>5</v>
       </c>
-      <c r="C48" s="145" t="s">
-        <v>44</v>
-      </c>
-      <c r="D48" s="145"/>
+      <c r="C48" s="141" t="s">
+        <v>42</v>
+      </c>
+      <c r="D48" s="141"/>
       <c r="E48" s="51"/>
       <c r="F48" s="51"/>
       <c r="G48" s="51"/>
@@ -7197,23 +7187,23 @@
       <c r="C49" s="9">
         <v>1</v>
       </c>
-      <c r="D49" s="146" t="s">
+      <c r="D49" s="142" t="s">
         <v>16</v>
       </c>
-      <c r="E49" s="146"/>
-      <c r="F49" s="146"/>
+      <c r="E49" s="142"/>
+      <c r="F49" s="142"/>
       <c r="G49" s="12">
         <v>90</v>
       </c>
       <c r="H49" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I49" s="40">
         <f>G8</f>
         <v>0</v>
       </c>
       <c r="J49" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K49" s="12">
         <f>J5</f>
@@ -7244,23 +7234,23 @@
       <c r="C50" s="9">
         <v>2</v>
       </c>
-      <c r="D50" s="145" t="s">
-        <v>35</v>
-      </c>
-      <c r="E50" s="145"/>
-      <c r="F50" s="145"/>
+      <c r="D50" s="141" t="s">
+        <v>34</v>
+      </c>
+      <c r="E50" s="141"/>
+      <c r="F50" s="141"/>
       <c r="G50" s="12">
         <v>80</v>
       </c>
       <c r="H50" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I50" s="4">
         <f>I8</f>
         <v>0</v>
       </c>
       <c r="J50" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K50" s="12">
         <f>J5</f>
@@ -7292,7 +7282,7 @@
         <v>3</v>
       </c>
       <c r="D51" s="51" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E51" s="51"/>
       <c r="F51" s="51"/>
@@ -7300,14 +7290,14 @@
         <v>25</v>
       </c>
       <c r="H51" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I51" s="12">
         <f>E8</f>
         <v>0</v>
       </c>
       <c r="J51" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K51" s="12">
         <f>J5</f>
@@ -7339,7 +7329,7 @@
         <v>4</v>
       </c>
       <c r="D52" s="61" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E52" s="61"/>
       <c r="F52" s="61"/>
@@ -7347,14 +7337,14 @@
         <v>80</v>
       </c>
       <c r="H52" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I52" s="60">
         <f>K8</f>
         <v>0</v>
       </c>
       <c r="J52" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K52" s="12">
         <f>J5</f>
@@ -7385,23 +7375,23 @@
       <c r="C53" s="9">
         <v>5</v>
       </c>
-      <c r="D53" s="143" t="s">
+      <c r="D53" s="139" t="s">
         <v>18</v>
       </c>
-      <c r="E53" s="143"/>
-      <c r="F53" s="143"/>
+      <c r="E53" s="139"/>
+      <c r="F53" s="139"/>
       <c r="G53" s="12">
         <v>25</v>
       </c>
       <c r="H53" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I53" s="12">
         <f>E8</f>
         <v>0</v>
       </c>
       <c r="J53" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K53" s="12">
         <f>J5</f>
@@ -7432,23 +7422,23 @@
       <c r="C54" s="9">
         <v>6</v>
       </c>
-      <c r="D54" s="143" t="s">
+      <c r="D54" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="E54" s="143"/>
-      <c r="F54" s="143"/>
+      <c r="E54" s="139"/>
+      <c r="F54" s="139"/>
       <c r="G54" s="12">
         <v>25</v>
       </c>
       <c r="H54" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I54" s="12">
         <f>E8</f>
         <v>0</v>
       </c>
       <c r="J54" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K54" s="12">
         <f>J5</f>
@@ -7479,23 +7469,23 @@
       <c r="C55" s="9">
         <v>7</v>
       </c>
-      <c r="D55" s="155" t="s">
-        <v>74</v>
-      </c>
-      <c r="E55" s="155"/>
-      <c r="F55" s="155"/>
+      <c r="D55" s="143" t="s">
+        <v>68</v>
+      </c>
+      <c r="E55" s="143"/>
+      <c r="F55" s="143"/>
       <c r="G55" s="12">
         <v>25</v>
       </c>
       <c r="H55" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I55" s="12">
         <f>K8</f>
         <v>0</v>
       </c>
       <c r="J55" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K55" s="12">
         <f>J5</f>
@@ -7523,23 +7513,23 @@
       <c r="C56" s="9">
         <v>8</v>
       </c>
-      <c r="D56" s="143" t="s">
-        <v>31</v>
-      </c>
-      <c r="E56" s="143"/>
-      <c r="F56" s="143"/>
+      <c r="D56" s="139" t="s">
+        <v>30</v>
+      </c>
+      <c r="E56" s="139"/>
+      <c r="F56" s="139"/>
       <c r="G56" s="12">
         <v>40</v>
       </c>
       <c r="H56" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I56" s="12">
         <f>E8</f>
         <v>0</v>
       </c>
       <c r="J56" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K56" s="12">
         <f>J5</f>
@@ -7570,23 +7560,23 @@
       <c r="C57" s="9">
         <v>9</v>
       </c>
-      <c r="D57" s="143" t="s">
+      <c r="D57" s="139" t="s">
         <v>26</v>
       </c>
-      <c r="E57" s="143"/>
-      <c r="F57" s="143"/>
+      <c r="E57" s="139"/>
+      <c r="F57" s="139"/>
       <c r="G57" s="12">
         <v>2</v>
       </c>
       <c r="H57" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I57" s="12">
         <f>E8</f>
         <v>0</v>
       </c>
       <c r="J57" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K57" s="12">
         <f>J5</f>
@@ -7617,11 +7607,11 @@
       <c r="C58" s="9">
         <v>10</v>
       </c>
-      <c r="D58" s="143" t="s">
-        <v>32</v>
-      </c>
-      <c r="E58" s="143"/>
-      <c r="F58" s="143"/>
+      <c r="D58" s="139" t="s">
+        <v>31</v>
+      </c>
+      <c r="E58" s="139"/>
+      <c r="F58" s="139"/>
       <c r="G58" s="51"/>
       <c r="H58" s="51"/>
       <c r="I58" s="51"/>
@@ -7687,17 +7677,17 @@
     </row>
     <row r="61" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="54"/>
-      <c r="C61" s="143" t="s">
+      <c r="C61" s="139" t="s">
         <v>1</v>
       </c>
-      <c r="D61" s="143"/>
-      <c r="E61" s="143"/>
-      <c r="F61" s="143"/>
-      <c r="G61" s="143"/>
-      <c r="H61" s="143"/>
-      <c r="I61" s="143"/>
-      <c r="J61" s="143"/>
-      <c r="K61" s="143"/>
+      <c r="D61" s="139"/>
+      <c r="E61" s="139"/>
+      <c r="F61" s="139"/>
+      <c r="G61" s="139"/>
+      <c r="H61" s="139"/>
+      <c r="I61" s="139"/>
+      <c r="J61" s="139"/>
+      <c r="K61" s="139"/>
       <c r="L61" s="51"/>
       <c r="M61" s="51"/>
       <c r="N61" s="51"/>
@@ -7738,23 +7728,23 @@
       <c r="C63" s="9">
         <v>1</v>
       </c>
-      <c r="D63" s="143" t="s">
-        <v>34</v>
-      </c>
-      <c r="E63" s="143"/>
-      <c r="F63" s="143"/>
+      <c r="D63" s="139" t="s">
+        <v>33</v>
+      </c>
+      <c r="E63" s="139"/>
+      <c r="F63" s="139"/>
       <c r="G63" s="12">
         <v>25</v>
       </c>
       <c r="H63" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I63" s="12">
         <f>$E$22</f>
         <v>0</v>
       </c>
       <c r="J63" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K63" s="12">
         <f>J5</f>
@@ -7795,7 +7785,7 @@
       <c r="K64" s="12"/>
       <c r="L64" s="53"/>
       <c r="M64" s="8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="P64" s="51"/>
       <c r="Q64" s="12"/>
@@ -7810,23 +7800,23 @@
       <c r="C65" s="9">
         <v>3</v>
       </c>
-      <c r="D65" s="143" t="s">
-        <v>32</v>
-      </c>
-      <c r="E65" s="143"/>
-      <c r="F65" s="143"/>
+      <c r="D65" s="139" t="s">
+        <v>31</v>
+      </c>
+      <c r="E65" s="139"/>
+      <c r="F65" s="139"/>
       <c r="G65" s="27">
         <v>0.16</v>
       </c>
       <c r="H65" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I65" s="12">
         <f>$E$22</f>
         <v>0</v>
       </c>
       <c r="J65" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K65" s="12">
         <f>J5</f>
@@ -7839,8 +7829,8 @@
         <f>PRODUCT(G65,I65,K65)</f>
         <v>0</v>
       </c>
-      <c r="N65" s="142"/>
-      <c r="O65" s="142"/>
+      <c r="N65" s="138"/>
+      <c r="O65" s="138"/>
       <c r="P65" s="51"/>
       <c r="Q65" s="12">
         <f>M65</f>
@@ -7859,11 +7849,11 @@
       <c r="C66" s="32">
         <v>4</v>
       </c>
-      <c r="D66" s="143" t="s">
+      <c r="D66" s="139" t="s">
         <v>14</v>
       </c>
-      <c r="E66" s="143"/>
-      <c r="F66" s="143"/>
+      <c r="E66" s="139"/>
+      <c r="F66" s="139"/>
       <c r="G66" s="51"/>
       <c r="H66" s="51"/>
       <c r="I66" s="51"/>
@@ -7871,14 +7861,14 @@
       <c r="K66" s="51"/>
       <c r="L66" s="51"/>
       <c r="M66" s="51"/>
-      <c r="N66" s="142"/>
-      <c r="O66" s="142"/>
+      <c r="N66" s="138"/>
+      <c r="O66" s="138"/>
       <c r="P66" s="51"/>
       <c r="Q66" s="12">
         <v>1</v>
       </c>
       <c r="R66" s="51" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="S66" s="51"/>
       <c r="T66" s="44"/>
@@ -7890,11 +7880,11 @@
       <c r="C67" s="9">
         <v>5</v>
       </c>
-      <c r="D67" s="143" t="s">
+      <c r="D67" s="139" t="s">
         <v>3</v>
       </c>
-      <c r="E67" s="143"/>
-      <c r="F67" s="143"/>
+      <c r="E67" s="139"/>
+      <c r="F67" s="139"/>
       <c r="G67" s="51"/>
       <c r="H67" s="51"/>
       <c r="I67" s="51"/>
@@ -7921,7 +7911,7 @@
         <v>6</v>
       </c>
       <c r="D68" s="119" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E68" s="119"/>
       <c r="F68" s="119"/>
@@ -7929,14 +7919,14 @@
         <v>10</v>
       </c>
       <c r="H68" s="121" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I68" s="12">
         <f>$E$22</f>
         <v>0</v>
       </c>
       <c r="J68" s="121" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K68" s="120">
         <f>J5</f>
@@ -7969,7 +7959,7 @@
         <v>7</v>
       </c>
       <c r="D69" s="119" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E69" s="119"/>
       <c r="F69" s="119"/>
@@ -7977,14 +7967,14 @@
         <v>20</v>
       </c>
       <c r="H69" s="121" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I69" s="12">
         <f>$E$22</f>
         <v>0</v>
       </c>
       <c r="J69" s="121" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K69" s="120">
         <f>J5</f>
@@ -8060,10 +8050,6 @@
     <row r="72" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D30:F30"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="K5:N5"/>
     <mergeCell ref="O5:R5"/>
@@ -8086,6 +8072,10 @@
     <mergeCell ref="D42:F42"/>
     <mergeCell ref="D43:F43"/>
     <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D30:F30"/>
     <mergeCell ref="C46:D46"/>
     <mergeCell ref="D56:F56"/>
     <mergeCell ref="C48:D48"/>

--- a/Исходный_Шаблон_Весь_период.xlsx
+++ b/Исходный_Шаблон_Весь_период.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORK\Repository\github.com\daily_duty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF190B9B-E997-49DE-8FA8-D5AF3F26F770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30913910-1429-4E4A-831D-38C66B04B45E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="495" windowWidth="25065" windowHeight="13380" tabRatio="721" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="495" windowWidth="25065" windowHeight="13380" tabRatio="721" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="График" sheetId="12" r:id="rId1"/>
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="75">
   <si>
     <t>=</t>
   </si>
@@ -329,6 +329,9 @@
   </si>
   <si>
     <t>График дежурств отъезд 22 августа 2026г</t>
+  </si>
+  <si>
+    <t>Кофе</t>
   </si>
 </sst>
 </file>
@@ -880,7 +883,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1203,9 +1206,6 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1247,68 +1247,68 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1645,18 +1645,18 @@
       <c r="B2" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="130">
+      <c r="C2" s="129">
         <v>1</v>
       </c>
-      <c r="D2" s="159" t="s">
+      <c r="D2" s="138" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="160"/>
-      <c r="I2" s="160"/>
-      <c r="J2" s="160"/>
+      <c r="E2" s="139"/>
+      <c r="F2" s="139"/>
+      <c r="G2" s="139"/>
+      <c r="H2" s="139"/>
+      <c r="I2" s="139"/>
+      <c r="J2" s="139"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="51"/>
@@ -1667,9 +1667,9 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="161"/>
-      <c r="G3" s="161"/>
-      <c r="H3" s="161"/>
+      <c r="F3" s="140"/>
+      <c r="G3" s="140"/>
+      <c r="H3" s="140"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -1698,13 +1698,13 @@
       <c r="N4" s="51"/>
     </row>
     <row r="5" spans="1:33" ht="56.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="131" t="s">
+      <c r="B5" s="130" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="131" t="s">
+      <c r="C5" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="129" t="s">
+      <c r="D5" s="128" t="s">
         <v>53</v>
       </c>
       <c r="E5" s="48"/>
@@ -1804,7 +1804,7 @@
       <c r="N7" s="51"/>
     </row>
     <row r="8" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="162">
+      <c r="A8" s="141">
         <v>5</v>
       </c>
       <c r="B8" s="57" t="str">
@@ -1815,7 +1815,7 @@
         <v>22</v>
       </c>
       <c r="D8" s="65"/>
-      <c r="E8" s="134" t="s">
+      <c r="E8" s="133" t="s">
         <v>29</v>
       </c>
       <c r="F8" s="88"/>
@@ -1847,7 +1847,7 @@
       <c r="AG8" s="51"/>
     </row>
     <row r="9" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="158"/>
+      <c r="A9" s="137"/>
       <c r="B9" s="58">
         <f>F6</f>
         <v>22</v>
@@ -1891,7 +1891,7 @@
       <c r="AE9" s="26"/>
     </row>
     <row r="10" spans="1:33" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="158"/>
+      <c r="A10" s="137"/>
       <c r="B10" s="59"/>
       <c r="C10" s="93" t="s">
         <v>42</v>
@@ -1899,7 +1899,7 @@
       <c r="D10" s="107">
         <v>3</v>
       </c>
-      <c r="E10" s="135" t="s">
+      <c r="E10" s="134" t="s">
         <v>16</v>
       </c>
       <c r="F10" s="74" t="s">
@@ -1932,7 +1932,7 @@
       <c r="AE10" s="26"/>
     </row>
     <row r="11" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="158"/>
+      <c r="A11" s="137"/>
       <c r="B11" s="58" t="str">
         <f>G5</f>
         <v>воскресенье</v>
@@ -1940,10 +1940,10 @@
       <c r="C11" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="126">
+      <c r="D11" s="125">
         <v>3</v>
       </c>
-      <c r="E11" s="132" t="s">
+      <c r="E11" s="131" t="s">
         <v>37</v>
       </c>
       <c r="F11" s="78"/>
@@ -1976,7 +1976,7 @@
       <c r="AE11" s="26"/>
     </row>
     <row r="12" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="158"/>
+      <c r="A12" s="137"/>
       <c r="B12" s="58">
         <f>G6</f>
         <v>23</v>
@@ -1984,7 +1984,7 @@
       <c r="C12" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="127">
+      <c r="D12" s="126">
         <v>3</v>
       </c>
       <c r="E12" s="69" t="s">
@@ -2020,15 +2020,15 @@
       <c r="AE12" s="26"/>
     </row>
     <row r="13" spans="1:33" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="158"/>
+      <c r="A13" s="137"/>
       <c r="B13" s="59"/>
       <c r="C13" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="127">
+      <c r="D13" s="126">
         <v>3</v>
       </c>
-      <c r="E13" s="133" t="s">
+      <c r="E13" s="132" t="s">
         <v>67</v>
       </c>
       <c r="F13" s="102"/>
@@ -2061,7 +2061,7 @@
       <c r="AE13" s="26"/>
     </row>
     <row r="14" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="158"/>
+      <c r="A14" s="137"/>
       <c r="B14" s="58" t="str">
         <f>H5</f>
         <v>понедельник</v>
@@ -2069,10 +2069,10 @@
       <c r="C14" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="127">
+      <c r="D14" s="126">
         <v>3</v>
       </c>
-      <c r="E14" s="134" t="s">
+      <c r="E14" s="133" t="s">
         <v>29</v>
       </c>
       <c r="F14" s="90"/>
@@ -2105,7 +2105,7 @@
       <c r="AE14" s="26"/>
     </row>
     <row r="15" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="158"/>
+      <c r="A15" s="137"/>
       <c r="B15" s="58">
         <f>H6</f>
         <v>24</v>
@@ -2113,7 +2113,7 @@
       <c r="C15" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="127">
+      <c r="D15" s="126">
         <v>3</v>
       </c>
       <c r="E15" s="69" t="s">
@@ -2149,15 +2149,15 @@
       <c r="AE15" s="26"/>
     </row>
     <row r="16" spans="1:33" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="158"/>
+      <c r="A16" s="137"/>
       <c r="B16" s="59"/>
       <c r="C16" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="127">
+      <c r="D16" s="126">
         <v>3</v>
       </c>
-      <c r="E16" s="135" t="s">
+      <c r="E16" s="134" t="s">
         <v>34</v>
       </c>
       <c r="F16" s="96"/>
@@ -2190,7 +2190,7 @@
       <c r="AE16" s="26"/>
     </row>
     <row r="17" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="158"/>
+      <c r="A17" s="137"/>
       <c r="B17" s="58" t="str">
         <f>I5</f>
         <v>вторник</v>
@@ -2198,10 +2198,10 @@
       <c r="C17" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="127">
+      <c r="D17" s="126">
         <v>3</v>
       </c>
-      <c r="E17" s="132" t="s">
+      <c r="E17" s="131" t="s">
         <v>66</v>
       </c>
       <c r="F17" s="90"/>
@@ -2234,7 +2234,7 @@
       <c r="AE17" s="26"/>
     </row>
     <row r="18" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="158"/>
+      <c r="A18" s="137"/>
       <c r="B18" s="58">
         <f>I6</f>
         <v>25</v>
@@ -2242,7 +2242,7 @@
       <c r="C18" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="127">
+      <c r="D18" s="126">
         <v>3</v>
       </c>
       <c r="E18" s="69" t="s">
@@ -2278,13 +2278,13 @@
       <c r="AE18" s="26"/>
     </row>
     <row r="19" spans="1:33" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="158"/>
+      <c r="A19" s="137"/>
       <c r="B19" s="59"/>
       <c r="C19" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="127"/>
-      <c r="E19" s="133"/>
+      <c r="D19" s="126"/>
+      <c r="E19" s="132"/>
       <c r="F19" s="96"/>
       <c r="G19" s="96"/>
       <c r="H19" s="102"/>
@@ -2313,7 +2313,7 @@
       <c r="AE19" s="26"/>
     </row>
     <row r="20" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="158"/>
+      <c r="A20" s="137"/>
       <c r="B20" s="58">
         <f>J5</f>
         <v>0</v>
@@ -2321,8 +2321,8 @@
       <c r="C20" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="127"/>
-      <c r="E20" s="134"/>
+      <c r="D20" s="126"/>
+      <c r="E20" s="133"/>
       <c r="F20" s="90"/>
       <c r="G20" s="90"/>
       <c r="H20" s="108"/>
@@ -2351,7 +2351,7 @@
       <c r="AE20" s="26"/>
     </row>
     <row r="21" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="158"/>
+      <c r="A21" s="137"/>
       <c r="B21" s="58">
         <f>J6</f>
         <v>0</v>
@@ -2359,7 +2359,7 @@
       <c r="C21" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="127"/>
+      <c r="D21" s="126"/>
       <c r="E21" s="69"/>
       <c r="F21" s="70"/>
       <c r="G21" s="70"/>
@@ -2389,13 +2389,13 @@
       <c r="AE21" s="26"/>
     </row>
     <row r="22" spans="1:33" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="158"/>
+      <c r="A22" s="137"/>
       <c r="B22" s="59"/>
       <c r="C22" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="127"/>
-      <c r="E22" s="135"/>
+      <c r="D22" s="126"/>
+      <c r="E22" s="134"/>
       <c r="F22" s="96"/>
       <c r="G22" s="96"/>
       <c r="H22" s="110"/>
@@ -2424,7 +2424,7 @@
       <c r="AE22" s="26"/>
     </row>
     <row r="23" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="158"/>
+      <c r="A23" s="137"/>
       <c r="B23" s="58">
         <f>K5</f>
         <v>0</v>
@@ -2432,8 +2432,8 @@
       <c r="C23" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="127"/>
-      <c r="E23" s="132"/>
+      <c r="D23" s="126"/>
+      <c r="E23" s="131"/>
       <c r="F23" s="91"/>
       <c r="G23" s="91"/>
       <c r="H23" s="91"/>
@@ -2462,7 +2462,7 @@
       <c r="AE23" s="26"/>
     </row>
     <row r="24" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="158"/>
+      <c r="A24" s="137"/>
       <c r="B24" s="58">
         <f>K6</f>
         <v>0</v>
@@ -2470,7 +2470,7 @@
       <c r="C24" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D24" s="127"/>
+      <c r="D24" s="126"/>
       <c r="E24" s="69"/>
       <c r="F24" s="68"/>
       <c r="G24" s="68"/>
@@ -2500,13 +2500,13 @@
       <c r="AE24" s="26"/>
     </row>
     <row r="25" spans="1:33" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="158"/>
+      <c r="A25" s="137"/>
       <c r="B25" s="59"/>
       <c r="C25" s="59" t="s">
         <v>42</v>
       </c>
       <c r="D25" s="107"/>
-      <c r="E25" s="133"/>
+      <c r="E25" s="132"/>
       <c r="F25" s="97"/>
       <c r="G25" s="97"/>
       <c r="H25" s="97"/>
@@ -2535,7 +2535,7 @@
       <c r="AE25" s="26"/>
     </row>
     <row r="26" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="158"/>
+      <c r="A26" s="137"/>
       <c r="B26" s="58">
         <f>L5</f>
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>22</v>
       </c>
       <c r="D26" s="101"/>
-      <c r="E26" s="134"/>
+      <c r="E26" s="133"/>
       <c r="F26" s="91"/>
       <c r="G26" s="91"/>
       <c r="H26" s="91"/>
@@ -2573,7 +2573,7 @@
       <c r="AE26" s="36"/>
     </row>
     <row r="27" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="158"/>
+      <c r="A27" s="137"/>
       <c r="B27" s="58">
         <f>L6</f>
         <v>0</v>
@@ -2611,13 +2611,13 @@
       <c r="AE27" s="36"/>
     </row>
     <row r="28" spans="1:33" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="158"/>
+      <c r="A28" s="137"/>
       <c r="B28" s="59"/>
       <c r="C28" s="59" t="s">
         <v>42</v>
       </c>
       <c r="D28" s="107"/>
-      <c r="E28" s="135"/>
+      <c r="E28" s="134"/>
       <c r="F28" s="97"/>
       <c r="G28" s="97"/>
       <c r="H28" s="97"/>
@@ -2646,7 +2646,7 @@
       <c r="AE28" s="36"/>
     </row>
     <row r="29" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="158">
+      <c r="A29" s="137">
         <v>4</v>
       </c>
       <c r="B29" s="58">
@@ -2687,7 +2687,7 @@
       <c r="AF29" s="36"/>
     </row>
     <row r="30" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="158"/>
+      <c r="A30" s="137"/>
       <c r="B30" s="58">
         <f>M6</f>
         <v>0</v>
@@ -2695,7 +2695,7 @@
       <c r="C30" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="127"/>
+      <c r="D30" s="126"/>
       <c r="E30" s="69"/>
       <c r="F30" s="68"/>
       <c r="G30" s="68"/>
@@ -2726,13 +2726,13 @@
       <c r="AF30" s="36"/>
     </row>
     <row r="31" spans="1:33" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="158"/>
+      <c r="A31" s="137"/>
       <c r="B31" s="59"/>
       <c r="C31" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="128"/>
-      <c r="E31" s="136"/>
+      <c r="D31" s="127"/>
+      <c r="E31" s="135"/>
       <c r="F31" s="97"/>
       <c r="G31" s="97"/>
       <c r="H31" s="97"/>
@@ -2762,7 +2762,7 @@
       <c r="AF31" s="36"/>
     </row>
     <row r="32" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="158"/>
+      <c r="A32" s="137"/>
       <c r="B32" s="58">
         <f>N5</f>
         <v>0</v>
@@ -2770,8 +2770,8 @@
       <c r="C32" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D32" s="126"/>
-      <c r="E32" s="134"/>
+      <c r="D32" s="125"/>
+      <c r="E32" s="133"/>
       <c r="F32" s="91"/>
       <c r="G32" s="91"/>
       <c r="H32" s="91"/>
@@ -2801,7 +2801,7 @@
       <c r="AG32" s="36"/>
     </row>
     <row r="33" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="158"/>
+      <c r="A33" s="137"/>
       <c r="B33" s="58">
         <f>N6</f>
         <v>0</v>
@@ -2809,7 +2809,7 @@
       <c r="C33" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D33" s="127"/>
+      <c r="D33" s="126"/>
       <c r="E33" s="69"/>
       <c r="F33" s="68"/>
       <c r="G33" s="68"/>
@@ -2840,13 +2840,13 @@
       <c r="AG33" s="36"/>
     </row>
     <row r="34" spans="1:33" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="158"/>
+      <c r="A34" s="137"/>
       <c r="B34" s="59"/>
       <c r="C34" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D34" s="128"/>
-      <c r="E34" s="135"/>
+      <c r="D34" s="127"/>
+      <c r="E34" s="134"/>
       <c r="F34" s="97"/>
       <c r="G34" s="97"/>
       <c r="H34" s="97"/>
@@ -2873,7 +2873,7 @@
       <c r="AC34" s="97"/>
     </row>
     <row r="35" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="158"/>
+      <c r="A35" s="137"/>
       <c r="B35" s="58">
         <f>O5</f>
         <v>0</v>
@@ -2881,7 +2881,7 @@
       <c r="C35" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D35" s="126"/>
+      <c r="D35" s="125"/>
       <c r="E35" s="99"/>
       <c r="F35" s="91"/>
       <c r="G35" s="91"/>
@@ -2909,7 +2909,7 @@
       <c r="AC35" s="67"/>
     </row>
     <row r="36" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="158"/>
+      <c r="A36" s="137"/>
       <c r="B36" s="58">
         <f>O6</f>
         <v>0</v>
@@ -2917,7 +2917,7 @@
       <c r="C36" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D36" s="127"/>
+      <c r="D36" s="126"/>
       <c r="E36" s="69"/>
       <c r="F36" s="68"/>
       <c r="G36" s="68"/>
@@ -2945,13 +2945,13 @@
       <c r="AC36" s="67"/>
     </row>
     <row r="37" spans="1:33" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="158"/>
+      <c r="A37" s="137"/>
       <c r="B37" s="59"/>
       <c r="C37" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D37" s="128"/>
-      <c r="E37" s="136"/>
+      <c r="D37" s="127"/>
+      <c r="E37" s="135"/>
       <c r="F37" s="97"/>
       <c r="G37" s="97"/>
       <c r="H37" s="97"/>
@@ -2978,7 +2978,7 @@
       <c r="AC37" s="97"/>
     </row>
     <row r="38" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="158"/>
+      <c r="A38" s="137"/>
       <c r="B38" s="58">
         <f>P5</f>
         <v>0</v>
@@ -2986,8 +2986,8 @@
       <c r="C38" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D38" s="126"/>
-      <c r="E38" s="134"/>
+      <c r="D38" s="125"/>
+      <c r="E38" s="133"/>
       <c r="F38" s="91"/>
       <c r="G38" s="91"/>
       <c r="H38" s="91"/>
@@ -3014,7 +3014,7 @@
       <c r="AC38" s="67"/>
     </row>
     <row r="39" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="158"/>
+      <c r="A39" s="137"/>
       <c r="B39" s="58">
         <f>P6</f>
         <v>0</v>
@@ -3022,7 +3022,7 @@
       <c r="C39" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D39" s="127"/>
+      <c r="D39" s="126"/>
       <c r="E39" s="69"/>
       <c r="F39" s="68"/>
       <c r="G39" s="68"/>
@@ -3050,13 +3050,13 @@
       <c r="AC39" s="67"/>
     </row>
     <row r="40" spans="1:33" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="158"/>
+      <c r="A40" s="137"/>
       <c r="B40" s="59"/>
       <c r="C40" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="128"/>
-      <c r="E40" s="135"/>
+      <c r="D40" s="127"/>
+      <c r="E40" s="134"/>
       <c r="F40" s="97"/>
       <c r="G40" s="97"/>
       <c r="H40" s="97"/>
@@ -3083,7 +3083,7 @@
       <c r="AC40" s="97"/>
     </row>
     <row r="41" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="158"/>
+      <c r="A41" s="137"/>
       <c r="B41" s="58">
         <f>Q5</f>
         <v>0</v>
@@ -3091,7 +3091,7 @@
       <c r="C41" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D41" s="126"/>
+      <c r="D41" s="125"/>
       <c r="E41" s="99"/>
       <c r="F41" s="91"/>
       <c r="G41" s="91"/>
@@ -3119,7 +3119,7 @@
       <c r="AC41" s="67"/>
     </row>
     <row r="42" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="158"/>
+      <c r="A42" s="137"/>
       <c r="B42" s="58">
         <f>Q6</f>
         <v>0</v>
@@ -3127,7 +3127,7 @@
       <c r="C42" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D42" s="127"/>
+      <c r="D42" s="126"/>
       <c r="E42" s="69"/>
       <c r="F42" s="68"/>
       <c r="G42" s="68"/>
@@ -3155,13 +3155,13 @@
       <c r="AC42" s="67"/>
     </row>
     <row r="43" spans="1:33" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="158"/>
+      <c r="A43" s="137"/>
       <c r="B43" s="59"/>
       <c r="C43" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D43" s="128"/>
-      <c r="E43" s="136"/>
+      <c r="D43" s="127"/>
+      <c r="E43" s="135"/>
       <c r="F43" s="97"/>
       <c r="G43" s="97"/>
       <c r="H43" s="97"/>
@@ -3188,7 +3188,7 @@
       <c r="AC43" s="97"/>
     </row>
     <row r="44" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="158"/>
+      <c r="A44" s="137"/>
       <c r="B44" s="58">
         <f>R5</f>
         <v>0</v>
@@ -3196,8 +3196,8 @@
       <c r="C44" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D44" s="126"/>
-      <c r="E44" s="134"/>
+      <c r="D44" s="125"/>
+      <c r="E44" s="133"/>
       <c r="F44" s="91"/>
       <c r="G44" s="91"/>
       <c r="H44" s="91"/>
@@ -3224,7 +3224,7 @@
       <c r="AC44" s="67"/>
     </row>
     <row r="45" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="158"/>
+      <c r="A45" s="137"/>
       <c r="B45" s="58">
         <f>R6</f>
         <v>0</v>
@@ -3232,7 +3232,7 @@
       <c r="C45" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D45" s="127"/>
+      <c r="D45" s="126"/>
       <c r="E45" s="69"/>
       <c r="F45" s="68"/>
       <c r="G45" s="68"/>
@@ -3260,13 +3260,13 @@
       <c r="AC45" s="67"/>
     </row>
     <row r="46" spans="1:33" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="158"/>
+      <c r="A46" s="137"/>
       <c r="B46" s="59"/>
       <c r="C46" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D46" s="128"/>
-      <c r="E46" s="135"/>
+      <c r="D46" s="127"/>
+      <c r="E46" s="134"/>
       <c r="F46" s="97"/>
       <c r="G46" s="97"/>
       <c r="H46" s="97"/>
@@ -3293,7 +3293,7 @@
       <c r="AC46" s="97"/>
     </row>
     <row r="47" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="158"/>
+      <c r="A47" s="137"/>
       <c r="B47" s="58">
         <f>S5</f>
         <v>0</v>
@@ -3301,7 +3301,7 @@
       <c r="C47" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D47" s="126"/>
+      <c r="D47" s="125"/>
       <c r="E47" s="99"/>
       <c r="F47" s="91"/>
       <c r="G47" s="91"/>
@@ -3329,7 +3329,7 @@
       <c r="AC47" s="67"/>
     </row>
     <row r="48" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="158"/>
+      <c r="A48" s="137"/>
       <c r="B48" s="58">
         <f>S6</f>
         <v>0</v>
@@ -3337,7 +3337,7 @@
       <c r="C48" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="127"/>
+      <c r="D48" s="126"/>
       <c r="E48" s="69"/>
       <c r="F48" s="68"/>
       <c r="G48" s="68"/>
@@ -3365,13 +3365,13 @@
       <c r="AC48" s="67"/>
     </row>
     <row r="49" spans="1:29" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="158"/>
+      <c r="A49" s="137"/>
       <c r="B49" s="59"/>
       <c r="C49" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="128"/>
-      <c r="E49" s="136"/>
+      <c r="D49" s="127"/>
+      <c r="E49" s="135"/>
       <c r="F49" s="97"/>
       <c r="G49" s="97"/>
       <c r="H49" s="97"/>
@@ -3398,7 +3398,7 @@
       <c r="AC49" s="97"/>
     </row>
     <row r="50" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="158"/>
+      <c r="A50" s="137"/>
       <c r="B50" s="58">
         <f>T5</f>
         <v>0</v>
@@ -3406,8 +3406,8 @@
       <c r="C50" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D50" s="126"/>
-      <c r="E50" s="134"/>
+      <c r="D50" s="125"/>
+      <c r="E50" s="133"/>
       <c r="F50" s="91"/>
       <c r="G50" s="91"/>
       <c r="H50" s="91"/>
@@ -3434,7 +3434,7 @@
       <c r="AC50" s="67"/>
     </row>
     <row r="51" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="158"/>
+      <c r="A51" s="137"/>
       <c r="B51" s="58">
         <f>T6</f>
         <v>0</v>
@@ -3442,7 +3442,7 @@
       <c r="C51" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D51" s="127"/>
+      <c r="D51" s="126"/>
       <c r="E51" s="69"/>
       <c r="F51" s="68"/>
       <c r="G51" s="68"/>
@@ -3470,13 +3470,13 @@
       <c r="AC51" s="67"/>
     </row>
     <row r="52" spans="1:29" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="158"/>
+      <c r="A52" s="137"/>
       <c r="B52" s="59"/>
       <c r="C52" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D52" s="128"/>
-      <c r="E52" s="135"/>
+      <c r="D52" s="127"/>
+      <c r="E52" s="134"/>
       <c r="F52" s="97"/>
       <c r="G52" s="97"/>
       <c r="H52" s="97"/>
@@ -3503,7 +3503,7 @@
       <c r="AC52" s="97"/>
     </row>
     <row r="53" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="158"/>
+      <c r="A53" s="137"/>
       <c r="B53" s="58">
         <f>U5</f>
         <v>0</v>
@@ -3511,7 +3511,7 @@
       <c r="C53" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D53" s="126"/>
+      <c r="D53" s="125"/>
       <c r="E53" s="99"/>
       <c r="F53" s="91"/>
       <c r="G53" s="91"/>
@@ -3539,7 +3539,7 @@
       <c r="AC53" s="67"/>
     </row>
     <row r="54" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="158"/>
+      <c r="A54" s="137"/>
       <c r="B54" s="58">
         <f>U6</f>
         <v>0</v>
@@ -3547,7 +3547,7 @@
       <c r="C54" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D54" s="127"/>
+      <c r="D54" s="126"/>
       <c r="E54" s="69"/>
       <c r="F54" s="68"/>
       <c r="G54" s="68"/>
@@ -3575,13 +3575,13 @@
       <c r="AC54" s="67"/>
     </row>
     <row r="55" spans="1:29" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="158"/>
+      <c r="A55" s="137"/>
       <c r="B55" s="59"/>
       <c r="C55" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D55" s="128"/>
-      <c r="E55" s="136"/>
+      <c r="D55" s="127"/>
+      <c r="E55" s="135"/>
       <c r="F55" s="97"/>
       <c r="G55" s="97"/>
       <c r="H55" s="97"/>
@@ -3608,7 +3608,7 @@
       <c r="AC55" s="97"/>
     </row>
     <row r="56" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="158"/>
+      <c r="A56" s="137"/>
       <c r="B56" s="58">
         <f>V5</f>
         <v>0</v>
@@ -3616,8 +3616,8 @@
       <c r="C56" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D56" s="126"/>
-      <c r="E56" s="134"/>
+      <c r="D56" s="125"/>
+      <c r="E56" s="133"/>
       <c r="F56" s="91"/>
       <c r="G56" s="91"/>
       <c r="H56" s="91"/>
@@ -3644,7 +3644,7 @@
       <c r="AC56" s="67"/>
     </row>
     <row r="57" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="158"/>
+      <c r="A57" s="137"/>
       <c r="B57" s="58">
         <f>V6</f>
         <v>0</v>
@@ -3652,7 +3652,7 @@
       <c r="C57" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D57" s="127"/>
+      <c r="D57" s="126"/>
       <c r="E57" s="69"/>
       <c r="F57" s="68"/>
       <c r="G57" s="68"/>
@@ -3680,13 +3680,13 @@
       <c r="AC57" s="67"/>
     </row>
     <row r="58" spans="1:29" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="158"/>
+      <c r="A58" s="137"/>
       <c r="B58" s="59"/>
       <c r="C58" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D58" s="128"/>
-      <c r="E58" s="135"/>
+      <c r="D58" s="127"/>
+      <c r="E58" s="134"/>
       <c r="F58" s="97"/>
       <c r="G58" s="97"/>
       <c r="H58" s="97"/>
@@ -3713,7 +3713,7 @@
       <c r="AC58" s="97"/>
     </row>
     <row r="59" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="158"/>
+      <c r="A59" s="137"/>
       <c r="B59" s="58">
         <f>W5</f>
         <v>0</v>
@@ -3721,7 +3721,7 @@
       <c r="C59" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D59" s="126"/>
+      <c r="D59" s="125"/>
       <c r="E59" s="99"/>
       <c r="F59" s="91"/>
       <c r="G59" s="91"/>
@@ -3749,7 +3749,7 @@
       <c r="AC59" s="67"/>
     </row>
     <row r="60" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="158"/>
+      <c r="A60" s="137"/>
       <c r="B60" s="58">
         <f>W6</f>
         <v>0</v>
@@ -3757,7 +3757,7 @@
       <c r="C60" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="127"/>
+      <c r="D60" s="126"/>
       <c r="E60" s="69"/>
       <c r="F60" s="68"/>
       <c r="G60" s="68"/>
@@ -3785,13 +3785,13 @@
       <c r="AC60" s="67"/>
     </row>
     <row r="61" spans="1:29" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="158"/>
+      <c r="A61" s="137"/>
       <c r="B61" s="59"/>
       <c r="C61" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D61" s="128"/>
-      <c r="E61" s="136"/>
+      <c r="D61" s="127"/>
+      <c r="E61" s="135"/>
       <c r="F61" s="97"/>
       <c r="G61" s="97"/>
       <c r="H61" s="97"/>
@@ -3818,7 +3818,7 @@
       <c r="AC61" s="97"/>
     </row>
     <row r="62" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="158"/>
+      <c r="A62" s="137"/>
       <c r="B62" s="58">
         <f>X5</f>
         <v>0</v>
@@ -3826,8 +3826,8 @@
       <c r="C62" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D62" s="126"/>
-      <c r="E62" s="134"/>
+      <c r="D62" s="125"/>
+      <c r="E62" s="133"/>
       <c r="F62" s="91"/>
       <c r="G62" s="91"/>
       <c r="H62" s="91"/>
@@ -3854,7 +3854,7 @@
       <c r="AC62" s="67"/>
     </row>
     <row r="63" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="158"/>
+      <c r="A63" s="137"/>
       <c r="B63" s="58">
         <f>X6</f>
         <v>0</v>
@@ -3862,7 +3862,7 @@
       <c r="C63" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D63" s="127"/>
+      <c r="D63" s="126"/>
       <c r="E63" s="69"/>
       <c r="F63" s="68"/>
       <c r="G63" s="68"/>
@@ -3890,13 +3890,13 @@
       <c r="AC63" s="67"/>
     </row>
     <row r="64" spans="1:29" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="158"/>
+      <c r="A64" s="137"/>
       <c r="B64" s="59"/>
       <c r="C64" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D64" s="128"/>
-      <c r="E64" s="135"/>
+      <c r="D64" s="127"/>
+      <c r="E64" s="134"/>
       <c r="F64" s="97"/>
       <c r="G64" s="97"/>
       <c r="H64" s="97"/>
@@ -3923,7 +3923,7 @@
       <c r="AC64" s="97"/>
     </row>
     <row r="65" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="158"/>
+      <c r="A65" s="137"/>
       <c r="B65" s="58">
         <f>Y5</f>
         <v>0</v>
@@ -3931,7 +3931,7 @@
       <c r="C65" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D65" s="126"/>
+      <c r="D65" s="125"/>
       <c r="E65" s="99"/>
       <c r="F65" s="91"/>
       <c r="G65" s="91"/>
@@ -3959,7 +3959,7 @@
       <c r="AC65" s="67"/>
     </row>
     <row r="66" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="158"/>
+      <c r="A66" s="137"/>
       <c r="B66" s="58">
         <f>Y6</f>
         <v>0</v>
@@ -3967,7 +3967,7 @@
       <c r="C66" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D66" s="127"/>
+      <c r="D66" s="126"/>
       <c r="E66" s="69"/>
       <c r="F66" s="68"/>
       <c r="G66" s="68"/>
@@ -3995,13 +3995,13 @@
       <c r="AC66" s="67"/>
     </row>
     <row r="67" spans="1:29" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="158"/>
+      <c r="A67" s="137"/>
       <c r="B67" s="59"/>
       <c r="C67" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D67" s="128"/>
-      <c r="E67" s="136"/>
+      <c r="D67" s="127"/>
+      <c r="E67" s="135"/>
       <c r="F67" s="97"/>
       <c r="G67" s="97"/>
       <c r="H67" s="97"/>
@@ -4028,7 +4028,7 @@
       <c r="AC67" s="97"/>
     </row>
     <row r="68" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="158"/>
+      <c r="A68" s="137"/>
       <c r="B68" s="58">
         <f>Z5</f>
         <v>0</v>
@@ -4036,8 +4036,8 @@
       <c r="C68" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D68" s="126"/>
-      <c r="E68" s="134"/>
+      <c r="D68" s="125"/>
+      <c r="E68" s="133"/>
       <c r="F68" s="91"/>
       <c r="G68" s="91"/>
       <c r="H68" s="91"/>
@@ -4064,7 +4064,7 @@
       <c r="AC68" s="67"/>
     </row>
     <row r="69" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="158"/>
+      <c r="A69" s="137"/>
       <c r="B69" s="58">
         <f>Z6</f>
         <v>0</v>
@@ -4072,7 +4072,7 @@
       <c r="C69" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D69" s="127"/>
+      <c r="D69" s="126"/>
       <c r="E69" s="69"/>
       <c r="F69" s="68"/>
       <c r="G69" s="68"/>
@@ -4100,13 +4100,13 @@
       <c r="AC69" s="67"/>
     </row>
     <row r="70" spans="1:29" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="158"/>
+      <c r="A70" s="137"/>
       <c r="B70" s="59"/>
       <c r="C70" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D70" s="128"/>
-      <c r="E70" s="135"/>
+      <c r="D70" s="127"/>
+      <c r="E70" s="134"/>
       <c r="F70" s="97"/>
       <c r="G70" s="97"/>
       <c r="H70" s="97"/>
@@ -4133,7 +4133,7 @@
       <c r="AC70" s="97"/>
     </row>
     <row r="71" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="158"/>
+      <c r="A71" s="137"/>
       <c r="B71" s="58">
         <f>AA5</f>
         <v>0</v>
@@ -4141,7 +4141,7 @@
       <c r="C71" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D71" s="126"/>
+      <c r="D71" s="125"/>
       <c r="E71" s="99"/>
       <c r="F71" s="91"/>
       <c r="G71" s="91"/>
@@ -4169,7 +4169,7 @@
       <c r="AC71" s="67"/>
     </row>
     <row r="72" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="158"/>
+      <c r="A72" s="137"/>
       <c r="B72" s="58">
         <f>AA6</f>
         <v>0</v>
@@ -4177,7 +4177,7 @@
       <c r="C72" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D72" s="127"/>
+      <c r="D72" s="126"/>
       <c r="E72" s="69"/>
       <c r="F72" s="68"/>
       <c r="G72" s="68"/>
@@ -4205,13 +4205,13 @@
       <c r="AC72" s="67"/>
     </row>
     <row r="73" spans="1:29" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="158"/>
+      <c r="A73" s="137"/>
       <c r="B73" s="59"/>
       <c r="C73" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D73" s="128"/>
-      <c r="E73" s="136"/>
+      <c r="D73" s="127"/>
+      <c r="E73" s="135"/>
       <c r="F73" s="97"/>
       <c r="G73" s="97"/>
       <c r="H73" s="97"/>
@@ -4238,7 +4238,7 @@
       <c r="AC73" s="97"/>
     </row>
     <row r="74" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="158"/>
+      <c r="A74" s="137"/>
       <c r="B74" s="58">
         <f>AB5</f>
         <v>0</v>
@@ -4246,8 +4246,8 @@
       <c r="C74" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D74" s="126"/>
-      <c r="E74" s="134"/>
+      <c r="D74" s="125"/>
+      <c r="E74" s="133"/>
       <c r="F74" s="91"/>
       <c r="G74" s="91"/>
       <c r="H74" s="91"/>
@@ -4274,7 +4274,7 @@
       <c r="AC74" s="67"/>
     </row>
     <row r="75" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="158"/>
+      <c r="A75" s="137"/>
       <c r="B75" s="58">
         <f>AB6</f>
         <v>0</v>
@@ -4282,7 +4282,7 @@
       <c r="C75" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D75" s="127"/>
+      <c r="D75" s="126"/>
       <c r="E75" s="69"/>
       <c r="F75" s="68"/>
       <c r="G75" s="68"/>
@@ -4310,13 +4310,13 @@
       <c r="AC75" s="67"/>
     </row>
     <row r="76" spans="1:29" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="158"/>
+      <c r="A76" s="137"/>
       <c r="B76" s="59"/>
       <c r="C76" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D76" s="128"/>
-      <c r="E76" s="135"/>
+      <c r="D76" s="127"/>
+      <c r="E76" s="134"/>
       <c r="F76" s="97"/>
       <c r="G76" s="97"/>
       <c r="H76" s="97"/>
@@ -4343,7 +4343,7 @@
       <c r="AC76" s="115"/>
     </row>
     <row r="77" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="158"/>
+      <c r="A77" s="137"/>
       <c r="B77" s="58">
         <f>AC5</f>
         <v>0</v>
@@ -4351,7 +4351,7 @@
       <c r="C77" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D77" s="126"/>
+      <c r="D77" s="125"/>
       <c r="E77" s="108"/>
       <c r="F77" s="91"/>
       <c r="G77" s="91"/>
@@ -4386,7 +4386,7 @@
       <c r="C78" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D78" s="127"/>
+      <c r="D78" s="126"/>
       <c r="E78" s="69"/>
       <c r="F78" s="68"/>
       <c r="G78" s="68"/>
@@ -4418,7 +4418,7 @@
       <c r="C79" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D79" s="128"/>
+      <c r="D79" s="127"/>
       <c r="E79" s="110"/>
       <c r="F79" s="68"/>
       <c r="G79" s="68"/>
@@ -4585,7 +4585,7 @@
       <c r="Q2" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="R2" s="130">
+      <c r="R2" s="129">
         <f>График!C2</f>
         <v>1</v>
       </c>
@@ -4708,31 +4708,31 @@
       <c r="CP4" s="51"/>
     </row>
     <row r="5" spans="1:94" ht="35.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="147" t="s">
+      <c r="B5" s="142" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="147"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="147"/>
-      <c r="F5" s="147"/>
-      <c r="G5" s="147"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="148"/>
+      <c r="C5" s="142"/>
+      <c r="D5" s="142"/>
+      <c r="E5" s="142"/>
+      <c r="F5" s="142"/>
+      <c r="G5" s="142"/>
+      <c r="H5" s="142"/>
+      <c r="I5" s="146"/>
       <c r="J5" s="20">
         <v>1</v>
       </c>
-      <c r="K5" s="146" t="s">
+      <c r="K5" s="143" t="s">
         <v>58</v>
       </c>
-      <c r="L5" s="139"/>
-      <c r="M5" s="139"/>
-      <c r="N5" s="139"/>
-      <c r="O5" s="138" t="s">
+      <c r="L5" s="144"/>
+      <c r="M5" s="144"/>
+      <c r="N5" s="144"/>
+      <c r="O5" s="145" t="s">
         <v>72</v>
       </c>
-      <c r="P5" s="138"/>
-      <c r="Q5" s="138"/>
-      <c r="R5" s="138"/>
+      <c r="P5" s="145"/>
+      <c r="Q5" s="145"/>
+      <c r="R5" s="145"/>
       <c r="S5" s="17"/>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
@@ -5010,10 +5010,10 @@
       <c r="B8" s="10">
         <v>1</v>
       </c>
-      <c r="C8" s="149" t="s">
+      <c r="C8" s="147" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="149"/>
+      <c r="D8" s="147"/>
       <c r="E8" s="12">
         <f>SUM(G8,I8,K8)</f>
         <v>0</v>
@@ -5122,8 +5122,8 @@
     </row>
     <row r="9" spans="1:94" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B9" s="54"/>
-      <c r="C9" s="149"/>
-      <c r="D9" s="149"/>
+      <c r="C9" s="147"/>
+      <c r="D9" s="147"/>
       <c r="E9" s="12"/>
       <c r="F9" s="53"/>
       <c r="G9" s="38"/>
@@ -5264,18 +5264,18 @@
       <c r="B11" s="54">
         <v>2</v>
       </c>
-      <c r="C11" s="139" t="s">
+      <c r="C11" s="144" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="139"/>
+      <c r="D11" s="144"/>
       <c r="E11" s="37"/>
-      <c r="F11" s="139" t="s">
+      <c r="F11" s="144" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="139"/>
-      <c r="H11" s="139"/>
-      <c r="I11" s="139"/>
-      <c r="J11" s="139"/>
+      <c r="G11" s="144"/>
+      <c r="H11" s="144"/>
+      <c r="I11" s="144"/>
+      <c r="J11" s="144"/>
       <c r="K11" s="51"/>
       <c r="L11" s="51"/>
       <c r="M11" s="51"/>
@@ -5413,10 +5413,10 @@
       <c r="B14" s="49">
         <v>3</v>
       </c>
-      <c r="C14" s="140" t="s">
+      <c r="C14" s="150" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="140"/>
+      <c r="D14" s="150"/>
       <c r="E14" s="12">
         <f>SUM(G14,I14,K14,M14)</f>
         <v>0</v>
@@ -5442,7 +5442,7 @@
       <c r="L14" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="M14" s="137">
+      <c r="M14" s="136">
         <v>0</v>
       </c>
       <c r="N14" s="51"/>
@@ -5571,18 +5571,18 @@
       <c r="B17" s="54">
         <v>4</v>
       </c>
-      <c r="C17" s="139" t="s">
+      <c r="C17" s="144" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="139"/>
+      <c r="D17" s="144"/>
       <c r="E17" s="37"/>
-      <c r="F17" s="139" t="s">
+      <c r="F17" s="144" t="s">
         <v>23</v>
       </c>
-      <c r="G17" s="139"/>
-      <c r="H17" s="139"/>
-      <c r="I17" s="139"/>
-      <c r="J17" s="139"/>
+      <c r="G17" s="144"/>
+      <c r="H17" s="144"/>
+      <c r="I17" s="144"/>
+      <c r="J17" s="144"/>
       <c r="K17" s="51"/>
       <c r="L17" s="51"/>
       <c r="M17" s="51"/>
@@ -5720,10 +5720,10 @@
       <c r="B20" s="24">
         <v>5</v>
       </c>
-      <c r="C20" s="150" t="s">
+      <c r="C20" s="151" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="150"/>
+      <c r="D20" s="151"/>
       <c r="E20" s="12">
         <f>SUM(G20,I20,K20)</f>
         <v>0</v>
@@ -5843,14 +5843,14 @@
       <c r="F22" s="53"/>
       <c r="G22" s="12"/>
       <c r="H22" s="53"/>
-      <c r="I22" s="144" t="s">
+      <c r="I22" s="152" t="s">
         <v>24</v>
       </c>
-      <c r="J22" s="144"/>
-      <c r="K22" s="145" t="s">
+      <c r="J22" s="152"/>
+      <c r="K22" s="153" t="s">
         <v>55</v>
       </c>
-      <c r="L22" s="145"/>
+      <c r="L22" s="153"/>
       <c r="M22" s="51"/>
       <c r="N22" s="51"/>
       <c r="O22" s="51"/>
@@ -5892,15 +5892,15 @@
       <c r="F23" s="51"/>
       <c r="G23" s="51"/>
       <c r="H23" s="2"/>
-      <c r="I23" s="144" t="s">
+      <c r="I23" s="152" t="s">
         <v>54</v>
       </c>
-      <c r="J23" s="144"/>
-      <c r="K23" s="144" t="s">
+      <c r="J23" s="152"/>
+      <c r="K23" s="152" t="s">
         <v>56</v>
       </c>
-      <c r="L23" s="144"/>
-      <c r="M23" s="144"/>
+      <c r="L23" s="152"/>
+      <c r="M23" s="152"/>
       <c r="N23" s="51"/>
       <c r="O23" s="51"/>
       <c r="P23" s="51"/>
@@ -5943,17 +5943,17 @@
       <c r="H24" s="51"/>
       <c r="I24" s="53"/>
       <c r="J24" s="51"/>
-      <c r="K24" s="145"/>
-      <c r="L24" s="145"/>
+      <c r="K24" s="153"/>
+      <c r="L24" s="153"/>
       <c r="M24" s="51"/>
       <c r="N24" s="51"/>
       <c r="O24" s="51"/>
       <c r="P24" s="51"/>
-      <c r="Q24" s="139" t="s">
+      <c r="Q24" s="144" t="s">
         <v>5</v>
       </c>
-      <c r="R24" s="139"/>
-      <c r="S24" s="139"/>
+      <c r="R24" s="144"/>
+      <c r="S24" s="144"/>
       <c r="T24" s="51" t="s">
         <v>2</v>
       </c>
@@ -6081,11 +6081,11 @@
       <c r="C27" s="9">
         <v>1</v>
       </c>
-      <c r="D27" s="142" t="s">
+      <c r="D27" s="149" t="s">
         <v>29</v>
       </c>
-      <c r="E27" s="142"/>
-      <c r="F27" s="142"/>
+      <c r="E27" s="149"/>
+      <c r="F27" s="149"/>
       <c r="G27" s="12">
         <v>90</v>
       </c>
@@ -6150,11 +6150,11 @@
       <c r="C28" s="9">
         <v>2</v>
       </c>
-      <c r="D28" s="141" t="s">
+      <c r="D28" s="148" t="s">
         <v>37</v>
       </c>
-      <c r="E28" s="141"/>
-      <c r="F28" s="141"/>
+      <c r="E28" s="148"/>
+      <c r="F28" s="148"/>
       <c r="G28" s="12">
         <v>90</v>
       </c>
@@ -6288,11 +6288,11 @@
       <c r="C30" s="9">
         <v>4</v>
       </c>
-      <c r="D30" s="156" t="s">
+      <c r="D30" s="159" t="s">
         <v>66</v>
       </c>
-      <c r="E30" s="157"/>
-      <c r="F30" s="157"/>
+      <c r="E30" s="160"/>
+      <c r="F30" s="160"/>
       <c r="G30" s="12">
         <v>90</v>
       </c>
@@ -6357,11 +6357,11 @@
       <c r="C31" s="9">
         <v>5</v>
       </c>
-      <c r="D31" s="139" t="s">
+      <c r="D31" s="144" t="s">
         <v>36</v>
       </c>
-      <c r="E31" s="139"/>
-      <c r="F31" s="139"/>
+      <c r="E31" s="144"/>
+      <c r="F31" s="144"/>
       <c r="G31" s="12">
         <v>100</v>
       </c>
@@ -6433,11 +6433,11 @@
       <c r="C32" s="9">
         <v>6</v>
       </c>
-      <c r="D32" s="139" t="s">
+      <c r="D32" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="E32" s="139"/>
-      <c r="F32" s="139"/>
+      <c r="E32" s="144"/>
+      <c r="F32" s="144"/>
       <c r="G32" s="12">
         <v>2</v>
       </c>
@@ -6499,11 +6499,11 @@
       <c r="C33" s="9">
         <v>7</v>
       </c>
-      <c r="D33" s="139" t="s">
+      <c r="D33" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="E33" s="139"/>
-      <c r="F33" s="139"/>
+      <c r="E33" s="144"/>
+      <c r="F33" s="144"/>
       <c r="G33" s="12"/>
       <c r="H33" s="53"/>
       <c r="I33" s="12"/>
@@ -6592,10 +6592,10 @@
       <c r="B35" s="54">
         <v>2</v>
       </c>
-      <c r="C35" s="139" t="s">
+      <c r="C35" s="144" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="139"/>
+      <c r="D35" s="144"/>
       <c r="E35" s="51"/>
       <c r="F35" s="51"/>
       <c r="G35" s="51"/>
@@ -6685,18 +6685,18 @@
       <c r="B37" s="49">
         <v>3</v>
       </c>
-      <c r="C37" s="140" t="s">
+      <c r="C37" s="150" t="s">
         <v>12</v>
       </c>
-      <c r="D37" s="140"/>
+      <c r="D37" s="150"/>
       <c r="E37" s="51"/>
-      <c r="F37" s="139" t="s">
+      <c r="F37" s="144" t="s">
         <v>7</v>
       </c>
-      <c r="G37" s="139"/>
-      <c r="H37" s="139"/>
-      <c r="I37" s="139"/>
-      <c r="J37" s="139"/>
+      <c r="G37" s="144"/>
+      <c r="H37" s="144"/>
+      <c r="I37" s="144"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="51"/>
       <c r="L37" s="51"/>
       <c r="M37" s="51"/>
@@ -6737,11 +6737,11 @@
       <c r="C38" s="9">
         <v>1</v>
       </c>
-      <c r="D38" s="139" t="s">
+      <c r="D38" s="144" t="s">
         <v>15</v>
       </c>
-      <c r="E38" s="139"/>
-      <c r="F38" s="139"/>
+      <c r="E38" s="144"/>
+      <c r="F38" s="144"/>
       <c r="G38" s="12">
         <v>100</v>
       </c>
@@ -6806,11 +6806,11 @@
       <c r="C39" s="9">
         <v>2</v>
       </c>
-      <c r="D39" s="151" t="s">
+      <c r="D39" s="154" t="s">
         <v>39</v>
       </c>
-      <c r="E39" s="151"/>
-      <c r="F39" s="151"/>
+      <c r="E39" s="154"/>
+      <c r="F39" s="154"/>
       <c r="G39" s="18">
         <v>0.5</v>
       </c>
@@ -6872,11 +6872,11 @@
       <c r="C40" s="9">
         <v>3</v>
       </c>
-      <c r="D40" s="152" t="s">
+      <c r="D40" s="155" t="s">
         <v>28</v>
       </c>
-      <c r="E40" s="152"/>
-      <c r="F40" s="152"/>
+      <c r="E40" s="155"/>
+      <c r="F40" s="155"/>
       <c r="G40" s="18">
         <v>0.5</v>
       </c>
@@ -6916,11 +6916,11 @@
       <c r="C41" s="9">
         <v>4</v>
       </c>
-      <c r="D41" s="153" t="s">
+      <c r="D41" s="156" t="s">
         <v>47</v>
       </c>
-      <c r="E41" s="154"/>
-      <c r="F41" s="155"/>
+      <c r="E41" s="157"/>
+      <c r="F41" s="158"/>
       <c r="G41" s="18">
         <v>0.5</v>
       </c>
@@ -6960,11 +6960,11 @@
       <c r="C42" s="9">
         <v>5</v>
       </c>
-      <c r="D42" s="139" t="s">
+      <c r="D42" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="139"/>
-      <c r="F42" s="139"/>
+      <c r="E42" s="144"/>
+      <c r="F42" s="144"/>
       <c r="G42" s="12">
         <v>2</v>
       </c>
@@ -7007,11 +7007,11 @@
       <c r="C43" s="9">
         <v>6</v>
       </c>
-      <c r="D43" s="139" t="s">
+      <c r="D43" s="144" t="s">
         <v>8</v>
       </c>
-      <c r="E43" s="139"/>
-      <c r="F43" s="139"/>
+      <c r="E43" s="144"/>
+      <c r="F43" s="144"/>
       <c r="G43" s="14">
         <v>0.25</v>
       </c>
@@ -7056,11 +7056,11 @@
       <c r="C44" s="9">
         <v>7</v>
       </c>
-      <c r="D44" s="139" t="s">
+      <c r="D44" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="E44" s="139"/>
-      <c r="F44" s="139"/>
+      <c r="E44" s="144"/>
+      <c r="F44" s="144"/>
       <c r="G44" s="51"/>
       <c r="H44" s="51"/>
       <c r="I44" s="51"/>
@@ -7109,10 +7109,10 @@
       <c r="B46" s="54">
         <v>4</v>
       </c>
-      <c r="C46" s="139" t="s">
+      <c r="C46" s="144" t="s">
         <v>13</v>
       </c>
-      <c r="D46" s="139"/>
+      <c r="D46" s="144"/>
       <c r="E46" s="51"/>
       <c r="F46" s="51"/>
       <c r="G46" s="51"/>
@@ -7159,10 +7159,10 @@
       <c r="B48" s="19">
         <v>5</v>
       </c>
-      <c r="C48" s="141" t="s">
+      <c r="C48" s="148" t="s">
         <v>42</v>
       </c>
-      <c r="D48" s="141"/>
+      <c r="D48" s="148"/>
       <c r="E48" s="51"/>
       <c r="F48" s="51"/>
       <c r="G48" s="51"/>
@@ -7187,11 +7187,11 @@
       <c r="C49" s="9">
         <v>1</v>
       </c>
-      <c r="D49" s="142" t="s">
+      <c r="D49" s="149" t="s">
         <v>16</v>
       </c>
-      <c r="E49" s="142"/>
-      <c r="F49" s="142"/>
+      <c r="E49" s="149"/>
+      <c r="F49" s="149"/>
       <c r="G49" s="12">
         <v>90</v>
       </c>
@@ -7234,11 +7234,11 @@
       <c r="C50" s="9">
         <v>2</v>
       </c>
-      <c r="D50" s="141" t="s">
+      <c r="D50" s="148" t="s">
         <v>34</v>
       </c>
-      <c r="E50" s="141"/>
-      <c r="F50" s="141"/>
+      <c r="E50" s="148"/>
+      <c r="F50" s="148"/>
       <c r="G50" s="12">
         <v>80</v>
       </c>
@@ -7375,11 +7375,11 @@
       <c r="C53" s="9">
         <v>5</v>
       </c>
-      <c r="D53" s="139" t="s">
+      <c r="D53" s="144" t="s">
         <v>18</v>
       </c>
-      <c r="E53" s="139"/>
-      <c r="F53" s="139"/>
+      <c r="E53" s="144"/>
+      <c r="F53" s="144"/>
       <c r="G53" s="12">
         <v>25</v>
       </c>
@@ -7422,11 +7422,11 @@
       <c r="C54" s="9">
         <v>6</v>
       </c>
-      <c r="D54" s="139" t="s">
+      <c r="D54" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E54" s="139"/>
-      <c r="F54" s="139"/>
+      <c r="E54" s="144"/>
+      <c r="F54" s="144"/>
       <c r="G54" s="12">
         <v>25</v>
       </c>
@@ -7469,11 +7469,11 @@
       <c r="C55" s="9">
         <v>7</v>
       </c>
-      <c r="D55" s="143" t="s">
+      <c r="D55" s="161" t="s">
         <v>68</v>
       </c>
-      <c r="E55" s="143"/>
-      <c r="F55" s="143"/>
+      <c r="E55" s="161"/>
+      <c r="F55" s="161"/>
       <c r="G55" s="12">
         <v>25</v>
       </c>
@@ -7513,11 +7513,11 @@
       <c r="C56" s="9">
         <v>8</v>
       </c>
-      <c r="D56" s="139" t="s">
+      <c r="D56" s="144" t="s">
         <v>30</v>
       </c>
-      <c r="E56" s="139"/>
-      <c r="F56" s="139"/>
+      <c r="E56" s="144"/>
+      <c r="F56" s="144"/>
       <c r="G56" s="12">
         <v>40</v>
       </c>
@@ -7560,11 +7560,11 @@
       <c r="C57" s="9">
         <v>9</v>
       </c>
-      <c r="D57" s="139" t="s">
+      <c r="D57" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="E57" s="139"/>
-      <c r="F57" s="139"/>
+      <c r="E57" s="144"/>
+      <c r="F57" s="144"/>
       <c r="G57" s="12">
         <v>2</v>
       </c>
@@ -7607,11 +7607,11 @@
       <c r="C58" s="9">
         <v>10</v>
       </c>
-      <c r="D58" s="139" t="s">
+      <c r="D58" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="E58" s="139"/>
-      <c r="F58" s="139"/>
+      <c r="E58" s="144"/>
+      <c r="F58" s="144"/>
       <c r="G58" s="51"/>
       <c r="H58" s="51"/>
       <c r="I58" s="51"/>
@@ -7677,17 +7677,17 @@
     </row>
     <row r="61" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="54"/>
-      <c r="C61" s="139" t="s">
+      <c r="C61" s="144" t="s">
         <v>1</v>
       </c>
-      <c r="D61" s="139"/>
-      <c r="E61" s="139"/>
-      <c r="F61" s="139"/>
-      <c r="G61" s="139"/>
-      <c r="H61" s="139"/>
-      <c r="I61" s="139"/>
-      <c r="J61" s="139"/>
-      <c r="K61" s="139"/>
+      <c r="D61" s="144"/>
+      <c r="E61" s="144"/>
+      <c r="F61" s="144"/>
+      <c r="G61" s="144"/>
+      <c r="H61" s="144"/>
+      <c r="I61" s="144"/>
+      <c r="J61" s="144"/>
+      <c r="K61" s="144"/>
       <c r="L61" s="51"/>
       <c r="M61" s="51"/>
       <c r="N61" s="51"/>
@@ -7728,11 +7728,11 @@
       <c r="C63" s="9">
         <v>1</v>
       </c>
-      <c r="D63" s="139" t="s">
+      <c r="D63" s="144" t="s">
         <v>33</v>
       </c>
-      <c r="E63" s="139"/>
-      <c r="F63" s="139"/>
+      <c r="E63" s="144"/>
+      <c r="F63" s="144"/>
       <c r="G63" s="12">
         <v>25</v>
       </c>
@@ -7747,7 +7747,7 @@
         <v>38</v>
       </c>
       <c r="K63" s="12">
-        <f>J5</f>
+        <f>$J$5</f>
         <v>1</v>
       </c>
       <c r="L63" s="53" t="s">
@@ -7800,11 +7800,11 @@
       <c r="C65" s="9">
         <v>3</v>
       </c>
-      <c r="D65" s="139" t="s">
+      <c r="D65" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="E65" s="139"/>
-      <c r="F65" s="139"/>
+      <c r="E65" s="144"/>
+      <c r="F65" s="144"/>
       <c r="G65" s="27">
         <v>0.16</v>
       </c>
@@ -7819,7 +7819,7 @@
         <v>38</v>
       </c>
       <c r="K65" s="12">
-        <f>J5</f>
+        <f>$J$5</f>
         <v>1</v>
       </c>
       <c r="L65" s="53" t="s">
@@ -7829,8 +7829,8 @@
         <f>PRODUCT(G65,I65,K65)</f>
         <v>0</v>
       </c>
-      <c r="N65" s="138"/>
-      <c r="O65" s="138"/>
+      <c r="N65" s="145"/>
+      <c r="O65" s="145"/>
       <c r="P65" s="51"/>
       <c r="Q65" s="12">
         <f>M65</f>
@@ -7849,11 +7849,11 @@
       <c r="C66" s="32">
         <v>4</v>
       </c>
-      <c r="D66" s="139" t="s">
+      <c r="D66" s="144" t="s">
         <v>14</v>
       </c>
-      <c r="E66" s="139"/>
-      <c r="F66" s="139"/>
+      <c r="E66" s="144"/>
+      <c r="F66" s="144"/>
       <c r="G66" s="51"/>
       <c r="H66" s="51"/>
       <c r="I66" s="51"/>
@@ -7861,8 +7861,8 @@
       <c r="K66" s="51"/>
       <c r="L66" s="51"/>
       <c r="M66" s="51"/>
-      <c r="N66" s="138"/>
-      <c r="O66" s="138"/>
+      <c r="N66" s="145"/>
+      <c r="O66" s="145"/>
       <c r="P66" s="51"/>
       <c r="Q66" s="12">
         <v>1</v>
@@ -7880,11 +7880,11 @@
       <c r="C67" s="9">
         <v>5</v>
       </c>
-      <c r="D67" s="139" t="s">
+      <c r="D67" s="144" t="s">
         <v>3</v>
       </c>
-      <c r="E67" s="139"/>
-      <c r="F67" s="139"/>
+      <c r="E67" s="144"/>
+      <c r="F67" s="144"/>
       <c r="G67" s="51"/>
       <c r="H67" s="51"/>
       <c r="I67" s="51"/>
@@ -7904,7 +7904,7 @@
       <c r="U67" s="51"/>
       <c r="V67" s="51"/>
     </row>
-    <row r="68" spans="1:22" s="125" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:22" s="124" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="116"/>
       <c r="B68" s="117"/>
       <c r="C68" s="118">
@@ -7928,8 +7928,8 @@
       <c r="J68" s="121" t="s">
         <v>38</v>
       </c>
-      <c r="K68" s="120">
-        <f>J5</f>
+      <c r="K68" s="12">
+        <f>$J$5</f>
         <v>1</v>
       </c>
       <c r="L68" s="121" t="s">
@@ -7939,8 +7939,8 @@
         <f>PRODUCT(G68,I68,K68)</f>
         <v>0</v>
       </c>
-      <c r="N68" s="123"/>
-      <c r="O68" s="123"/>
+      <c r="N68" s="122"/>
+      <c r="O68" s="122"/>
       <c r="P68" s="119"/>
       <c r="Q68" s="12">
         <f>M68</f>
@@ -7948,11 +7948,11 @@
       </c>
       <c r="R68" s="119"/>
       <c r="S68" s="119"/>
-      <c r="T68" s="124"/>
+      <c r="T68" s="123"/>
       <c r="U68" s="119"/>
       <c r="V68" s="119"/>
     </row>
-    <row r="69" spans="1:22" s="125" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:22" s="124" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="116"/>
       <c r="B69" s="117"/>
       <c r="C69" s="118">
@@ -7976,8 +7976,8 @@
       <c r="J69" s="121" t="s">
         <v>38</v>
       </c>
-      <c r="K69" s="120">
-        <f>J5</f>
+      <c r="K69" s="12">
+        <f>$J$5</f>
         <v>1</v>
       </c>
       <c r="L69" s="121" t="s">
@@ -7987,37 +7987,58 @@
         <f>PRODUCT(G69,I69,K69)</f>
         <v>0</v>
       </c>
-      <c r="N69" s="123"/>
-      <c r="O69" s="123"/>
+      <c r="N69" s="122"/>
+      <c r="O69" s="122"/>
       <c r="P69" s="119"/>
       <c r="Q69" s="12"/>
       <c r="R69" s="119"/>
       <c r="S69" s="119"/>
-      <c r="T69" s="124"/>
+      <c r="T69" s="123"/>
       <c r="U69" s="119"/>
       <c r="V69" s="119"/>
     </row>
-    <row r="70" spans="1:22" s="125" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:22" s="124" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="116"/>
       <c r="B70" s="117"/>
-      <c r="C70" s="118"/>
-      <c r="D70" s="119"/>
+      <c r="C70" s="118">
+        <v>8</v>
+      </c>
+      <c r="D70" s="119" t="s">
+        <v>74</v>
+      </c>
       <c r="E70" s="119"/>
       <c r="F70" s="119"/>
-      <c r="G70" s="120"/>
-      <c r="H70" s="121"/>
-      <c r="I70" s="122"/>
-      <c r="J70" s="121"/>
-      <c r="K70" s="120"/>
-      <c r="L70" s="121"/>
-      <c r="M70" s="117"/>
-      <c r="N70" s="123"/>
-      <c r="O70" s="123"/>
+      <c r="G70" s="120">
+        <v>20</v>
+      </c>
+      <c r="H70" s="121" t="s">
+        <v>38</v>
+      </c>
+      <c r="I70" s="12">
+        <f>$E$22</f>
+        <v>0</v>
+      </c>
+      <c r="J70" s="121" t="s">
+        <v>38</v>
+      </c>
+      <c r="K70" s="12">
+        <f>$J$5</f>
+        <v>1</v>
+      </c>
+      <c r="L70" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="M70" s="117">
+        <f>PRODUCT(G70,I70,K70)</f>
+        <v>0</v>
+      </c>
+      <c r="N70" s="122"/>
+      <c r="O70" s="122"/>
       <c r="P70" s="119"/>
       <c r="Q70" s="12"/>
       <c r="R70" s="119"/>
       <c r="S70" s="119"/>
-      <c r="T70" s="124"/>
+      <c r="T70" s="123"/>
       <c r="U70" s="119"/>
       <c r="V70" s="119"/>
     </row>
@@ -8050,40 +8071,6 @@
     <row r="72" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="O5:R5"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="Q24:S24"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D55:F55"/>
     <mergeCell ref="N65:O65"/>
     <mergeCell ref="D66:F66"/>
     <mergeCell ref="N66:O66"/>
@@ -8100,6 +8087,40 @@
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="F37:J37"/>
     <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="Q24:S24"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="O5:R5"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="C8:D9"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.28999999999999998" top="0.25" bottom="0.31" header="0.37" footer="0.31"/>
   <pageSetup paperSize="9" scale="42" orientation="landscape" useFirstPageNumber="1" r:id="rId1"/>
